--- a/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
+++ b/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alecjones/Documents/GitHub/Alec_Jones_Honours/Jones_honours/01_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDA4FC1-031B-954A-8B55-95D2541FBC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAC8588-607A-8E47-81B3-352FD9DC8D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="1080" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,8 +29,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId9"/>
-    <pivotCache cacheId="15" r:id="rId10"/>
+    <pivotCache cacheId="86" r:id="rId9"/>
+    <pivotCache cacheId="87" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2487,6 +2487,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -3315,7 +3316,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="14" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="86" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:E46" firstHeaderRow="1" firstDataRow="4" firstDataCol="2"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
@@ -3563,7 +3564,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="15" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="87" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:I8" firstHeaderRow="1" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="48">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>

--- a/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
+++ b/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alecjones/Documents/GitHub/Alec_Jones_Honours/Jones_honours/01_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAC8588-607A-8E47-81B3-352FD9DC8D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFF6EE7-D92D-C144-BD10-D66DCACF43E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="1080" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5560" yWindow="22500" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMARY" sheetId="13" state="hidden" r:id="rId1"/>
@@ -29,8 +29,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="86" r:id="rId9"/>
-    <pivotCache cacheId="87" r:id="rId10"/>
+    <pivotCache cacheId="90" r:id="rId9"/>
+    <pivotCache cacheId="91" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3316,7 +3316,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="86" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="90" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:E46" firstHeaderRow="1" firstDataRow="4" firstDataCol="2"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
@@ -3564,7 +3564,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="87" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="91" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:I8" firstHeaderRow="1" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="48">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>

--- a/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
+++ b/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alecjones/Documents/GitHub/Alec_Jones_Honours/Jones_honours/01_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFF6EE7-D92D-C144-BD10-D66DCACF43E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D49540-2723-C24B-B5AE-FFEDC7B09620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5560" yWindow="22500" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,8 +29,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="90" r:id="rId9"/>
-    <pivotCache cacheId="91" r:id="rId10"/>
+    <pivotCache cacheId="158" r:id="rId9"/>
+    <pivotCache cacheId="159" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3316,7 +3316,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="90" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="158" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:E46" firstHeaderRow="1" firstDataRow="4" firstDataCol="2"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
@@ -3564,7 +3564,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="91" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="159" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:I8" firstHeaderRow="1" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="48">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
@@ -4925,7 +4925,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:CK1087"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
@@ -5182,7 +5181,7 @@
       <c r="CJ1" s="14"/>
       <c r="CK1" s="14"/>
     </row>
-    <row r="2" spans="1:89" s="6" customFormat="1" hidden="1">
+    <row r="2" spans="1:89" s="6" customFormat="1">
       <c r="A2" s="35"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5298,7 +5297,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:89" hidden="1">
+    <row r="3" spans="1:89">
       <c r="B3" s="54" t="s">
         <v>64</v>
       </c>
@@ -5357,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:89" hidden="1">
+    <row r="4" spans="1:89">
       <c r="B4" s="54" t="s">
         <v>64</v>
       </c>
@@ -5419,7 +5418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:89" hidden="1">
+    <row r="5" spans="1:89">
       <c r="B5" s="54" t="s">
         <v>64</v>
       </c>
@@ -5587,7 +5586,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:89" hidden="1">
+    <row r="8" spans="1:89">
       <c r="B8" s="54" t="s">
         <v>64</v>
       </c>
@@ -5643,7 +5642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:89" hidden="1">
+    <row r="9" spans="1:89">
       <c r="B9" s="54" t="s">
         <v>64</v>
       </c>
@@ -5705,7 +5704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:89" hidden="1">
+    <row r="10" spans="1:89">
       <c r="B10" s="54" t="s">
         <v>64</v>
       </c>
@@ -5761,7 +5760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:89" hidden="1">
+    <row r="11" spans="1:89">
       <c r="B11" s="54" t="s">
         <v>64</v>
       </c>
@@ -5817,7 +5816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:89" hidden="1">
+    <row r="12" spans="1:89">
       <c r="B12" s="54" t="s">
         <v>64</v>
       </c>
@@ -5873,7 +5872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:89" hidden="1">
+    <row r="13" spans="1:89">
       <c r="B13" s="54" t="s">
         <v>64</v>
       </c>
@@ -5929,7 +5928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:89" hidden="1">
+    <row r="14" spans="1:89">
       <c r="B14" s="54" t="s">
         <v>64</v>
       </c>
@@ -5985,7 +5984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:89" hidden="1">
+    <row r="15" spans="1:89">
       <c r="B15" s="54" t="s">
         <v>64</v>
       </c>
@@ -6041,7 +6040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:89" hidden="1">
+    <row r="16" spans="1:89">
       <c r="B16" s="54" t="s">
         <v>64</v>
       </c>
@@ -6097,7 +6096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:27" hidden="1">
+    <row r="17" spans="2:27">
       <c r="B17" s="54" t="s">
         <v>64</v>
       </c>
@@ -6265,7 +6264,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="2:27" hidden="1">
+    <row r="20" spans="2:27">
       <c r="B20" s="54" t="s">
         <v>64</v>
       </c>
@@ -6321,7 +6320,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:27" hidden="1">
+    <row r="21" spans="2:27">
       <c r="B21" s="54" t="s">
         <v>64</v>
       </c>
@@ -6377,7 +6376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="2:27" hidden="1">
+    <row r="22" spans="2:27">
       <c r="B22" s="54" t="s">
         <v>64</v>
       </c>
@@ -6433,7 +6432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:27" hidden="1">
+    <row r="23" spans="2:27">
       <c r="B23" s="54" t="s">
         <v>64</v>
       </c>
@@ -6489,7 +6488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:27" hidden="1">
+    <row r="24" spans="2:27">
       <c r="B24" s="54" t="s">
         <v>64</v>
       </c>
@@ -6545,7 +6544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:27" hidden="1">
+    <row r="25" spans="2:27">
       <c r="B25" s="54" t="s">
         <v>64</v>
       </c>
@@ -6601,7 +6600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="2:27" hidden="1">
+    <row r="26" spans="2:27">
       <c r="B26" s="54" t="s">
         <v>64</v>
       </c>
@@ -6657,7 +6656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:27" hidden="1">
+    <row r="27" spans="2:27">
       <c r="B27" s="54" t="s">
         <v>64</v>
       </c>
@@ -6713,7 +6712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="2:27" hidden="1">
+    <row r="28" spans="2:27">
       <c r="B28" s="54" t="s">
         <v>64</v>
       </c>
@@ -6775,7 +6774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:27" hidden="1">
+    <row r="29" spans="2:27">
       <c r="B29" s="54" t="s">
         <v>64</v>
       </c>
@@ -6831,7 +6830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:27" hidden="1">
+    <row r="30" spans="2:27">
       <c r="B30" s="54" t="s">
         <v>64</v>
       </c>
@@ -6890,7 +6889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:27" hidden="1">
+    <row r="31" spans="2:27">
       <c r="B31" s="54" t="s">
         <v>64</v>
       </c>
@@ -6946,7 +6945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:27" hidden="1">
+    <row r="32" spans="2:27">
       <c r="B32" s="54" t="s">
         <v>64</v>
       </c>
@@ -7005,7 +7004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:31" hidden="1">
+    <row r="33" spans="2:31">
       <c r="B33" s="54" t="s">
         <v>64</v>
       </c>
@@ -7067,7 +7066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:31" hidden="1">
+    <row r="34" spans="2:31">
       <c r="B34" s="54" t="s">
         <v>64</v>
       </c>
@@ -7123,7 +7122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:31" hidden="1">
+    <row r="35" spans="2:31">
       <c r="B35" s="54" t="s">
         <v>64</v>
       </c>
@@ -7179,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:31" hidden="1">
+    <row r="36" spans="2:31">
       <c r="B36" s="54" t="s">
         <v>64</v>
       </c>
@@ -7241,7 +7240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:31" hidden="1">
+    <row r="37" spans="2:31">
       <c r="B37" s="54" t="s">
         <v>64</v>
       </c>
@@ -7424,7 +7423,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="2:31" hidden="1">
+    <row r="40" spans="2:31">
       <c r="B40" s="54" t="s">
         <v>64</v>
       </c>
@@ -7480,7 +7479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="2:31" hidden="1">
+    <row r="41" spans="2:31">
       <c r="B41" s="54" t="s">
         <v>64</v>
       </c>
@@ -7536,7 +7535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:31" hidden="1">
+    <row r="42" spans="2:31">
       <c r="B42" s="54" t="s">
         <v>64</v>
       </c>
@@ -7592,7 +7591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:31" hidden="1">
+    <row r="43" spans="2:31">
       <c r="B43" s="54" t="s">
         <v>64</v>
       </c>
@@ -7648,7 +7647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:31" hidden="1">
+    <row r="44" spans="2:31">
       <c r="B44" s="54" t="s">
         <v>64</v>
       </c>
@@ -7707,7 +7706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:31" hidden="1">
+    <row r="45" spans="2:31">
       <c r="B45" s="54" t="s">
         <v>64</v>
       </c>
@@ -7766,7 +7765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:31" hidden="1">
+    <row r="46" spans="2:31">
       <c r="B46" s="54" t="s">
         <v>64</v>
       </c>
@@ -7831,7 +7830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:31" hidden="1">
+    <row r="47" spans="2:31">
       <c r="B47" s="54" t="s">
         <v>64</v>
       </c>
@@ -7887,7 +7886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:31" hidden="1">
+    <row r="48" spans="2:31">
       <c r="B48" s="54" t="s">
         <v>64</v>
       </c>
@@ -7943,7 +7942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:19" hidden="1">
+    <row r="49" spans="2:19">
       <c r="B49" s="54" t="s">
         <v>64</v>
       </c>
@@ -7999,7 +7998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="2:19" hidden="1">
+    <row r="50" spans="2:19">
       <c r="B50" s="54" t="s">
         <v>64</v>
       </c>
@@ -8055,7 +8054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="2:19" hidden="1">
+    <row r="51" spans="2:19">
       <c r="B51" s="54" t="s">
         <v>64</v>
       </c>
@@ -8111,7 +8110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:19" hidden="1">
+    <row r="52" spans="2:19">
       <c r="B52" s="54" t="s">
         <v>64</v>
       </c>
@@ -8167,7 +8166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:19" hidden="1">
+    <row r="53" spans="2:19">
       <c r="B53" s="54" t="s">
         <v>64</v>
       </c>
@@ -8223,7 +8222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:19" hidden="1">
+    <row r="54" spans="2:19">
       <c r="B54" s="54" t="s">
         <v>64</v>
       </c>
@@ -8279,7 +8278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:19" hidden="1">
+    <row r="55" spans="2:19">
       <c r="B55" s="54" t="s">
         <v>64</v>
       </c>
@@ -8447,7 +8446,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="2:19" hidden="1">
+    <row r="58" spans="2:19">
       <c r="B58" s="54" t="s">
         <v>64</v>
       </c>
@@ -8503,7 +8502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="2:19" hidden="1">
+    <row r="59" spans="2:19">
       <c r="B59" s="54" t="s">
         <v>64</v>
       </c>
@@ -8559,7 +8558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="2:19" hidden="1">
+    <row r="60" spans="2:19">
       <c r="B60" s="54" t="s">
         <v>64</v>
       </c>
@@ -8615,7 +8614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="2:19" hidden="1">
+    <row r="61" spans="2:19">
       <c r="B61" s="54" t="s">
         <v>64</v>
       </c>
@@ -8671,7 +8670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:19" hidden="1">
+    <row r="62" spans="2:19">
       <c r="B62" s="54" t="s">
         <v>64</v>
       </c>
@@ -8727,7 +8726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="2:19" hidden="1">
+    <row r="63" spans="2:19">
       <c r="B63" s="54" t="s">
         <v>64</v>
       </c>
@@ -8783,7 +8782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="2:19" hidden="1">
+    <row r="64" spans="2:19">
       <c r="B64" s="54" t="s">
         <v>64</v>
       </c>
@@ -8839,7 +8838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="2:30" hidden="1">
+    <row r="65" spans="2:30">
       <c r="B65" s="54" t="s">
         <v>64</v>
       </c>
@@ -8895,7 +8894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:30" hidden="1">
+    <row r="66" spans="2:30">
       <c r="B66" s="54" t="s">
         <v>64</v>
       </c>
@@ -8951,7 +8950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="2:30" hidden="1">
+    <row r="67" spans="2:30">
       <c r="B67" s="54" t="s">
         <v>64</v>
       </c>
@@ -9013,7 +9012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:30" hidden="1">
+    <row r="68" spans="2:30">
       <c r="B68" s="54" t="s">
         <v>64</v>
       </c>
@@ -9069,7 +9068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="2:30" hidden="1">
+    <row r="69" spans="2:30">
       <c r="B69" s="54" t="s">
         <v>64</v>
       </c>
@@ -9125,7 +9124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:30" hidden="1">
+    <row r="70" spans="2:30">
       <c r="B70" s="54" t="s">
         <v>64</v>
       </c>
@@ -9181,7 +9180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="2:30" hidden="1">
+    <row r="71" spans="2:30">
       <c r="B71" s="54" t="s">
         <v>64</v>
       </c>
@@ -9240,7 +9239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:30" hidden="1">
+    <row r="72" spans="2:30">
       <c r="B72" s="54" t="s">
         <v>64</v>
       </c>
@@ -9296,7 +9295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:30" hidden="1">
+    <row r="73" spans="2:30">
       <c r="B73" s="54" t="s">
         <v>64</v>
       </c>
@@ -9352,7 +9351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:30" hidden="1">
+    <row r="74" spans="2:30">
       <c r="B74" s="54" t="s">
         <v>64</v>
       </c>
@@ -9408,7 +9407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:30" hidden="1">
+    <row r="75" spans="2:30">
       <c r="B75" s="54" t="s">
         <v>64</v>
       </c>
@@ -9482,7 +9481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="2:30" hidden="1">
+    <row r="76" spans="2:30">
       <c r="B76" s="54" t="s">
         <v>64</v>
       </c>
@@ -9550,7 +9549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:30" hidden="1">
+    <row r="77" spans="2:30">
       <c r="B77" s="54" t="s">
         <v>64</v>
       </c>
@@ -9609,7 +9608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="2:30" hidden="1">
+    <row r="78" spans="2:30">
       <c r="B78" s="54" t="s">
         <v>64</v>
       </c>
@@ -9668,7 +9667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="2:30" hidden="1">
+    <row r="79" spans="2:30">
       <c r="B79" s="54" t="s">
         <v>64</v>
       </c>
@@ -9727,7 +9726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="2:30" hidden="1">
+    <row r="80" spans="2:30">
       <c r="B80" s="54" t="s">
         <v>64</v>
       </c>
@@ -9786,7 +9785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:27" hidden="1">
+    <row r="81" spans="2:27">
       <c r="B81" s="54" t="s">
         <v>64</v>
       </c>
@@ -9854,7 +9853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:27" hidden="1">
+    <row r="82" spans="2:27">
       <c r="B82" s="54" t="s">
         <v>64</v>
       </c>
@@ -9925,7 +9924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:27" hidden="1">
+    <row r="83" spans="2:27">
       <c r="B83" s="54" t="s">
         <v>64</v>
       </c>
@@ -10096,7 +10095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="2:27" hidden="1">
+    <row r="86" spans="2:27">
       <c r="B86" s="54" t="s">
         <v>64</v>
       </c>
@@ -10152,7 +10151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:27" hidden="1">
+    <row r="87" spans="2:27">
       <c r="B87" s="54" t="s">
         <v>64</v>
       </c>
@@ -10208,7 +10207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="2:27" hidden="1">
+    <row r="88" spans="2:27">
       <c r="B88" s="54" t="s">
         <v>64</v>
       </c>
@@ -10264,7 +10263,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:27" hidden="1">
+    <row r="89" spans="2:27">
       <c r="B89" s="54" t="s">
         <v>64</v>
       </c>
@@ -10332,7 +10331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:27" hidden="1">
+    <row r="90" spans="2:27">
       <c r="B90" s="54" t="s">
         <v>64</v>
       </c>
@@ -10388,7 +10387,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="2:27" hidden="1">
+    <row r="91" spans="2:27">
       <c r="B91" s="54" t="s">
         <v>64</v>
       </c>
@@ -10444,7 +10443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="2:27" hidden="1">
+    <row r="92" spans="2:27">
       <c r="B92" s="54" t="s">
         <v>64</v>
       </c>
@@ -10500,7 +10499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="2:27" hidden="1">
+    <row r="93" spans="2:27">
       <c r="B93" s="54" t="s">
         <v>64</v>
       </c>
@@ -10677,7 +10676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="2:27" hidden="1">
+    <row r="96" spans="2:27">
       <c r="B96" s="54" t="s">
         <v>64</v>
       </c>
@@ -10733,7 +10732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="2:26" hidden="1">
+    <row r="97" spans="2:26">
       <c r="B97" s="54" t="s">
         <v>64</v>
       </c>
@@ -10789,7 +10788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="2:26" hidden="1">
+    <row r="98" spans="2:26">
       <c r="B98" s="54" t="s">
         <v>64</v>
       </c>
@@ -10854,7 +10853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:26" hidden="1">
+    <row r="99" spans="2:26">
       <c r="B99" s="54" t="s">
         <v>64</v>
       </c>
@@ -10922,7 +10921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:26" hidden="1">
+    <row r="100" spans="2:26">
       <c r="B100" s="54" t="s">
         <v>64</v>
       </c>
@@ -10978,7 +10977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="2:26" hidden="1">
+    <row r="101" spans="2:26">
       <c r="B101" s="54" t="s">
         <v>64</v>
       </c>
@@ -11034,7 +11033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="2:26" hidden="1">
+    <row r="102" spans="2:26">
       <c r="B102" s="54" t="s">
         <v>64</v>
       </c>
@@ -11090,7 +11089,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="2:26" hidden="1">
+    <row r="103" spans="2:26">
       <c r="B103" s="54" t="s">
         <v>64</v>
       </c>
@@ -11146,7 +11145,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="2:26" hidden="1">
+    <row r="104" spans="2:26">
       <c r="B104" s="54" t="s">
         <v>64</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:26" hidden="1">
+    <row r="105" spans="2:26">
       <c r="B105" s="54" t="s">
         <v>64</v>
       </c>
@@ -11264,7 +11263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="2:26" hidden="1">
+    <row r="106" spans="2:26">
       <c r="B106" s="54" t="s">
         <v>64</v>
       </c>
@@ -11320,7 +11319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:26" hidden="1">
+    <row r="107" spans="2:26">
       <c r="B107" s="54" t="s">
         <v>64</v>
       </c>
@@ -11376,7 +11375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:26" hidden="1">
+    <row r="108" spans="2:26">
       <c r="B108" s="54" t="s">
         <v>64</v>
       </c>
@@ -11432,7 +11431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:26" hidden="1">
+    <row r="109" spans="2:26">
       <c r="B109" s="54" t="s">
         <v>64</v>
       </c>
@@ -11488,7 +11487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:26" hidden="1">
+    <row r="110" spans="2:26">
       <c r="B110" s="54" t="s">
         <v>64</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:26" hidden="1">
+    <row r="111" spans="2:26">
       <c r="B111" s="54" t="s">
         <v>64</v>
       </c>
@@ -11600,7 +11599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:26" hidden="1">
+    <row r="112" spans="2:26">
       <c r="B112" s="54" t="s">
         <v>64</v>
       </c>
@@ -11656,7 +11655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:32" hidden="1">
+    <row r="113" spans="2:32">
       <c r="B113" s="54" t="s">
         <v>64</v>
       </c>
@@ -11715,7 +11714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:32" hidden="1">
+    <row r="114" spans="2:32">
       <c r="B114" s="54" t="s">
         <v>64</v>
       </c>
@@ -11774,7 +11773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="2:32" hidden="1">
+    <row r="115" spans="2:32">
       <c r="B115" s="54" t="s">
         <v>64</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:32" hidden="1">
+    <row r="116" spans="2:32">
       <c r="B116" s="54" t="s">
         <v>64</v>
       </c>
@@ -11913,7 +11912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:32" hidden="1">
+    <row r="117" spans="2:32">
       <c r="B117" s="54" t="s">
         <v>64</v>
       </c>
@@ -11972,7 +11971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="2:32" hidden="1">
+    <row r="118" spans="2:32">
       <c r="B118" s="54" t="s">
         <v>64</v>
       </c>
@@ -12031,7 +12030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="2:32" hidden="1">
+    <row r="119" spans="2:32">
       <c r="B119" s="54" t="s">
         <v>64</v>
       </c>
@@ -12102,7 +12101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:32" hidden="1">
+    <row r="120" spans="2:32">
       <c r="B120" s="54" t="s">
         <v>64</v>
       </c>
@@ -12164,7 +12163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:32" hidden="1">
+    <row r="121" spans="2:32">
       <c r="B121" s="54" t="s">
         <v>64</v>
       </c>
@@ -12223,7 +12222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:32" hidden="1">
+    <row r="122" spans="2:32">
       <c r="B122" s="54" t="s">
         <v>64</v>
       </c>
@@ -12282,7 +12281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:32" hidden="1">
+    <row r="123" spans="2:32">
       <c r="B123" s="54" t="s">
         <v>64</v>
       </c>
@@ -12456,7 +12455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="2:32" hidden="1">
+    <row r="126" spans="2:32">
       <c r="B126" s="54" t="s">
         <v>64</v>
       </c>
@@ -12512,7 +12511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="2:32" hidden="1">
+    <row r="127" spans="2:32">
       <c r="B127" s="54" t="s">
         <v>64</v>
       </c>
@@ -12568,7 +12567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="2:32" hidden="1">
+    <row r="128" spans="2:32">
       <c r="B128" s="54" t="s">
         <v>64</v>
       </c>
@@ -12624,7 +12623,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="2:26" hidden="1">
+    <row r="129" spans="2:26">
       <c r="B129" s="54" t="s">
         <v>64</v>
       </c>
@@ -12695,7 +12694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="2:26" hidden="1">
+    <row r="130" spans="2:26">
       <c r="B130" s="54" t="s">
         <v>64</v>
       </c>
@@ -12751,7 +12750,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="2:26" hidden="1">
+    <row r="131" spans="2:26">
       <c r="B131" s="54" t="s">
         <v>64</v>
       </c>
@@ -12807,7 +12806,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="2:26" hidden="1">
+    <row r="132" spans="2:26">
       <c r="B132" s="54" t="s">
         <v>64</v>
       </c>
@@ -12863,7 +12862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="2:26" hidden="1">
+    <row r="133" spans="2:26">
       <c r="B133" s="54" t="s">
         <v>64</v>
       </c>
@@ -12928,7 +12927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="2:26" hidden="1">
+    <row r="134" spans="2:26">
       <c r="B134" s="54" t="s">
         <v>64</v>
       </c>
@@ -12984,7 +12983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="2:26" hidden="1">
+    <row r="135" spans="2:26">
       <c r="B135" s="54" t="s">
         <v>64</v>
       </c>
@@ -13040,7 +13039,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="2:26" hidden="1">
+    <row r="136" spans="2:26">
       <c r="B136" s="54" t="s">
         <v>64</v>
       </c>
@@ -13105,7 +13104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="2:26" hidden="1">
+    <row r="137" spans="2:26">
       <c r="B137" s="54" t="s">
         <v>64</v>
       </c>
@@ -13164,7 +13163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="2:26" hidden="1">
+    <row r="138" spans="2:26">
       <c r="B138" s="54" t="s">
         <v>64</v>
       </c>
@@ -13220,7 +13219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="2:26" hidden="1">
+    <row r="139" spans="2:26">
       <c r="B139" s="54" t="s">
         <v>64</v>
       </c>
@@ -13279,7 +13278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="2:26" hidden="1">
+    <row r="140" spans="2:26">
       <c r="B140" s="54" t="s">
         <v>64</v>
       </c>
@@ -13447,7 +13446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="2:26" hidden="1">
+    <row r="143" spans="2:26">
       <c r="B143" s="54" t="s">
         <v>64</v>
       </c>
@@ -13503,7 +13502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="2:26" hidden="1">
+    <row r="144" spans="2:26">
       <c r="B144" s="54" t="s">
         <v>64</v>
       </c>
@@ -13556,7 +13555,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="145" spans="2:27" hidden="1">
+    <row r="145" spans="2:27">
       <c r="B145" s="54" t="s">
         <v>64</v>
       </c>
@@ -13612,7 +13611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="2:27" hidden="1">
+    <row r="146" spans="2:27">
       <c r="B146" s="54" t="s">
         <v>64</v>
       </c>
@@ -13677,7 +13676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="2:27" hidden="1">
+    <row r="147" spans="2:27">
       <c r="B147" s="54" t="s">
         <v>64</v>
       </c>
@@ -13733,7 +13732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="2:27" hidden="1">
+    <row r="148" spans="2:27">
       <c r="B148" s="54" t="s">
         <v>64</v>
       </c>
@@ -13789,7 +13788,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" spans="2:27" hidden="1">
+    <row r="149" spans="2:27">
       <c r="B149" s="54" t="s">
         <v>64</v>
       </c>
@@ -13845,7 +13844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="2:27" hidden="1">
+    <row r="150" spans="2:27">
       <c r="B150" s="54" t="s">
         <v>64</v>
       </c>
@@ -13904,7 +13903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="2:27" hidden="1">
+    <row r="151" spans="2:27">
       <c r="B151" s="54" t="s">
         <v>64</v>
       </c>
@@ -13960,7 +13959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="2:27" hidden="1">
+    <row r="152" spans="2:27">
       <c r="B152" s="54" t="s">
         <v>64</v>
       </c>
@@ -14016,7 +14015,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="2:27" hidden="1">
+    <row r="153" spans="2:27">
       <c r="B153" s="54" t="s">
         <v>64</v>
       </c>
@@ -14078,7 +14077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="2:27" hidden="1">
+    <row r="154" spans="2:27">
       <c r="B154" s="54" t="s">
         <v>64</v>
       </c>
@@ -14134,7 +14133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="2:27" hidden="1">
+    <row r="155" spans="2:27">
       <c r="B155" s="54" t="s">
         <v>64</v>
       </c>
@@ -14190,7 +14189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="2:27" hidden="1">
+    <row r="156" spans="2:27">
       <c r="B156" s="54" t="s">
         <v>64</v>
       </c>
@@ -14246,7 +14245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="2:27" hidden="1">
+    <row r="157" spans="2:27">
       <c r="B157" s="54" t="s">
         <v>64</v>
       </c>
@@ -14305,7 +14304,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="158" spans="2:27" hidden="1">
+    <row r="158" spans="2:27">
       <c r="B158" s="54" t="s">
         <v>64</v>
       </c>
@@ -14367,7 +14366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="2:27" hidden="1">
+    <row r="159" spans="2:27">
       <c r="B159" s="54" t="s">
         <v>64</v>
       </c>
@@ -14488,7 +14487,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="2:27" hidden="1">
+    <row r="161" spans="2:27">
       <c r="B161" s="54" t="s">
         <v>64</v>
       </c>
@@ -14544,7 +14543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="2:27" hidden="1">
+    <row r="162" spans="2:27">
       <c r="B162" s="54" t="s">
         <v>64</v>
       </c>
@@ -14600,7 +14599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="2:27" hidden="1">
+    <row r="163" spans="2:27">
       <c r="B163" s="54" t="s">
         <v>64</v>
       </c>
@@ -14656,7 +14655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="2:27" hidden="1">
+    <row r="164" spans="2:27">
       <c r="B164" s="54" t="s">
         <v>64</v>
       </c>
@@ -14712,7 +14711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="2:27" hidden="1">
+    <row r="165" spans="2:27">
       <c r="B165" s="54" t="s">
         <v>64</v>
       </c>
@@ -14768,7 +14767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="2:27" hidden="1">
+    <row r="166" spans="2:27">
       <c r="B166" s="54" t="s">
         <v>64</v>
       </c>
@@ -14824,7 +14823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="2:27" hidden="1">
+    <row r="167" spans="2:27">
       <c r="B167" s="54" t="s">
         <v>64</v>
       </c>
@@ -14883,7 +14882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="2:27" hidden="1">
+    <row r="168" spans="2:27">
       <c r="B168" s="54" t="s">
         <v>64</v>
       </c>
@@ -14939,7 +14938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="2:27" hidden="1">
+    <row r="169" spans="2:27">
       <c r="B169" s="54" t="s">
         <v>64</v>
       </c>
@@ -14995,7 +14994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="2:27" hidden="1">
+    <row r="170" spans="2:27">
       <c r="B170" s="54" t="s">
         <v>64</v>
       </c>
@@ -15051,7 +15050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="2:27" hidden="1">
+    <row r="171" spans="2:27">
       <c r="B171" s="54" t="s">
         <v>64</v>
       </c>
@@ -15107,7 +15106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="2:27" hidden="1">
+    <row r="172" spans="2:27">
       <c r="B172" s="54" t="s">
         <v>64</v>
       </c>
@@ -15163,7 +15162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="2:27" hidden="1">
+    <row r="173" spans="2:27">
       <c r="B173" s="54" t="s">
         <v>64</v>
       </c>
@@ -15219,7 +15218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="2:27" hidden="1">
+    <row r="174" spans="2:27">
       <c r="B174" s="54" t="s">
         <v>64</v>
       </c>
@@ -15275,7 +15274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="2:27" hidden="1">
+    <row r="175" spans="2:27">
       <c r="B175" s="54" t="s">
         <v>64</v>
       </c>
@@ -15334,7 +15333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="2:27" hidden="1">
+    <row r="176" spans="2:27">
       <c r="B176" s="54" t="s">
         <v>64</v>
       </c>
@@ -15390,7 +15389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="2:25" hidden="1">
+    <row r="177" spans="2:25">
       <c r="B177" s="54" t="s">
         <v>64</v>
       </c>
@@ -15446,7 +15445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="2:25" hidden="1">
+    <row r="178" spans="2:25">
       <c r="B178" s="54" t="s">
         <v>64</v>
       </c>
@@ -15502,7 +15501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="2:25" hidden="1">
+    <row r="179" spans="2:25">
       <c r="B179" s="54" t="s">
         <v>64</v>
       </c>
@@ -15561,7 +15560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="2:25" hidden="1">
+    <row r="180" spans="2:25">
       <c r="B180" s="54" t="s">
         <v>64</v>
       </c>
@@ -15617,7 +15616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="2:25" hidden="1">
+    <row r="181" spans="2:25">
       <c r="B181" s="54" t="s">
         <v>64</v>
       </c>
@@ -15673,7 +15672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="2:25" hidden="1">
+    <row r="182" spans="2:25">
       <c r="B182" s="54" t="s">
         <v>64</v>
       </c>
@@ -15785,7 +15784,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="184" spans="2:25" hidden="1">
+    <row r="184" spans="2:25">
       <c r="B184" s="54" t="s">
         <v>64</v>
       </c>
@@ -15841,7 +15840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="2:25" hidden="1">
+    <row r="185" spans="2:25">
       <c r="B185" s="54" t="s">
         <v>64</v>
       </c>
@@ -15897,7 +15896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="2:25" hidden="1">
+    <row r="186" spans="2:25">
       <c r="B186" s="54" t="s">
         <v>64</v>
       </c>
@@ -15953,7 +15952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="2:25" hidden="1">
+    <row r="187" spans="2:25">
       <c r="B187" s="54" t="s">
         <v>64</v>
       </c>
@@ -16009,7 +16008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="2:25" hidden="1">
+    <row r="188" spans="2:25">
       <c r="B188" s="54" t="s">
         <v>64</v>
       </c>
@@ -16071,7 +16070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="2:25" hidden="1">
+    <row r="189" spans="2:25">
       <c r="B189" s="54" t="s">
         <v>64</v>
       </c>
@@ -16127,7 +16126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="2:25" hidden="1">
+    <row r="190" spans="2:25">
       <c r="B190" s="54" t="s">
         <v>64</v>
       </c>
@@ -16183,7 +16182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="2:25" hidden="1">
+    <row r="191" spans="2:25">
       <c r="B191" s="54" t="s">
         <v>64</v>
       </c>
@@ -16239,7 +16238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="2:25" hidden="1">
+    <row r="192" spans="2:25">
       <c r="B192" s="54" t="s">
         <v>64</v>
       </c>
@@ -16298,7 +16297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="2:29" hidden="1">
+    <row r="193" spans="2:29">
       <c r="B193" s="54" t="s">
         <v>64</v>
       </c>
@@ -16354,7 +16353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="2:29" hidden="1">
+    <row r="194" spans="2:29">
       <c r="B194" s="54" t="s">
         <v>64</v>
       </c>
@@ -16410,7 +16409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="2:29" hidden="1">
+    <row r="195" spans="2:29">
       <c r="B195" s="54" t="s">
         <v>64</v>
       </c>
@@ -16466,7 +16465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="2:29" hidden="1">
+    <row r="196" spans="2:29">
       <c r="B196" s="54" t="s">
         <v>64</v>
       </c>
@@ -16522,7 +16521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="2:29" hidden="1">
+    <row r="197" spans="2:29">
       <c r="B197" s="54" t="s">
         <v>64</v>
       </c>
@@ -16590,7 +16589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="2:29" hidden="1">
+    <row r="198" spans="2:29">
       <c r="B198" s="54" t="s">
         <v>64</v>
       </c>
@@ -16649,7 +16648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="2:29" hidden="1">
+    <row r="199" spans="2:29">
       <c r="B199" s="54" t="s">
         <v>64</v>
       </c>
@@ -16717,7 +16716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="2:29" hidden="1">
+    <row r="200" spans="2:29">
       <c r="B200" s="54" t="s">
         <v>64</v>
       </c>
@@ -16773,7 +16772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="2:29" hidden="1">
+    <row r="201" spans="2:29">
       <c r="B201" s="54" t="s">
         <v>64</v>
       </c>
@@ -16885,7 +16884,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="203" spans="2:29" hidden="1">
+    <row r="203" spans="2:29">
       <c r="B203" s="54" t="s">
         <v>64</v>
       </c>
@@ -16941,7 +16940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="2:29" hidden="1">
+    <row r="204" spans="2:29">
       <c r="B204" s="54" t="s">
         <v>64</v>
       </c>
@@ -16997,7 +16996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="2:29" hidden="1">
+    <row r="205" spans="2:29">
       <c r="B205" s="54" t="s">
         <v>64</v>
       </c>
@@ -17109,7 +17108,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="207" spans="2:29" hidden="1">
+    <row r="207" spans="2:29">
       <c r="B207" s="54" t="s">
         <v>64</v>
       </c>
@@ -17165,7 +17164,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="2:29" hidden="1">
+    <row r="208" spans="2:29">
       <c r="B208" s="54" t="s">
         <v>64</v>
       </c>
@@ -17221,7 +17220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="2:27" hidden="1">
+    <row r="209" spans="2:27">
       <c r="B209" s="54" t="s">
         <v>64</v>
       </c>
@@ -17280,7 +17279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="2:27" hidden="1">
+    <row r="210" spans="2:27">
       <c r="B210" s="54" t="s">
         <v>64</v>
       </c>
@@ -17336,7 +17335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="2:27" hidden="1">
+    <row r="211" spans="2:27">
       <c r="B211" s="54" t="s">
         <v>64</v>
       </c>
@@ -17392,7 +17391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="2:27" hidden="1">
+    <row r="212" spans="2:27">
       <c r="B212" s="54" t="s">
         <v>64</v>
       </c>
@@ -17448,7 +17447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="2:27" hidden="1">
+    <row r="213" spans="2:27">
       <c r="B213" s="54" t="s">
         <v>64</v>
       </c>
@@ -17504,7 +17503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="2:27" hidden="1">
+    <row r="214" spans="2:27">
       <c r="B214" s="54" t="s">
         <v>64</v>
       </c>
@@ -17560,7 +17559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="2:27" hidden="1">
+    <row r="215" spans="2:27">
       <c r="B215" s="54" t="s">
         <v>64</v>
       </c>
@@ -17616,7 +17615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="2:27" hidden="1">
+    <row r="216" spans="2:27">
       <c r="B216" s="54" t="s">
         <v>64</v>
       </c>
@@ -17678,7 +17677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="2:27" hidden="1">
+    <row r="217" spans="2:27">
       <c r="B217" s="54" t="s">
         <v>64</v>
       </c>
@@ -17734,7 +17733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="2:27" hidden="1">
+    <row r="218" spans="2:27">
       <c r="B218" s="54" t="s">
         <v>64</v>
       </c>
@@ -17790,7 +17789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="2:27" hidden="1">
+    <row r="219" spans="2:27">
       <c r="B219" s="54" t="s">
         <v>64</v>
       </c>
@@ -17846,7 +17845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="2:27" hidden="1">
+    <row r="220" spans="2:27">
       <c r="B220" s="54" t="s">
         <v>64</v>
       </c>
@@ -17905,7 +17904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="2:27" hidden="1">
+    <row r="221" spans="2:27">
       <c r="B221" s="54" t="s">
         <v>64</v>
       </c>
@@ -17964,7 +17963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="2:27" hidden="1">
+    <row r="222" spans="2:27">
       <c r="B222" s="54" t="s">
         <v>64</v>
       </c>
@@ -18023,7 +18022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="2:27" hidden="1">
+    <row r="223" spans="2:27">
       <c r="B223" s="54" t="s">
         <v>64</v>
       </c>
@@ -18135,7 +18134,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="225" spans="2:27" hidden="1">
+    <row r="225" spans="2:27">
       <c r="B225" s="54" t="s">
         <v>64</v>
       </c>
@@ -18191,7 +18190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="2:27" hidden="1">
+    <row r="226" spans="2:27">
       <c r="B226" s="54" t="s">
         <v>64</v>
       </c>
@@ -18247,7 +18246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="2:27" hidden="1">
+    <row r="227" spans="2:27">
       <c r="B227" s="54" t="s">
         <v>64</v>
       </c>
@@ -18359,7 +18358,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="229" spans="2:27" hidden="1">
+    <row r="229" spans="2:27">
       <c r="B229" s="54" t="s">
         <v>64</v>
       </c>
@@ -18415,7 +18414,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="2:27" hidden="1">
+    <row r="230" spans="2:27">
       <c r="B230" s="54" t="s">
         <v>64</v>
       </c>
@@ -18483,7 +18482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="2:27" hidden="1">
+    <row r="231" spans="2:27">
       <c r="B231" s="54" t="s">
         <v>64</v>
       </c>
@@ -18542,7 +18541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="2:27" hidden="1">
+    <row r="232" spans="2:27">
       <c r="B232" s="54" t="s">
         <v>64</v>
       </c>
@@ -18598,7 +18597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="2:27" hidden="1">
+    <row r="233" spans="2:27">
       <c r="B233" s="54" t="s">
         <v>64</v>
       </c>
@@ -18654,7 +18653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="2:27" hidden="1">
+    <row r="234" spans="2:27">
       <c r="B234" s="54" t="s">
         <v>64</v>
       </c>
@@ -18716,7 +18715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="2:27" hidden="1">
+    <row r="235" spans="2:27">
       <c r="B235" s="54" t="s">
         <v>64</v>
       </c>
@@ -18772,7 +18771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="2:27" hidden="1">
+    <row r="236" spans="2:27">
       <c r="B236" s="54" t="s">
         <v>64</v>
       </c>
@@ -18828,7 +18827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="2:27" hidden="1">
+    <row r="237" spans="2:27">
       <c r="B237" s="54" t="s">
         <v>64</v>
       </c>
@@ -18887,7 +18886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="2:27" hidden="1">
+    <row r="238" spans="2:27">
       <c r="B238" s="54" t="s">
         <v>64</v>
       </c>
@@ -18946,7 +18945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="2:27" hidden="1">
+    <row r="239" spans="2:27">
       <c r="B239" s="54" t="s">
         <v>64</v>
       </c>
@@ -19005,7 +19004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="2:27" hidden="1">
+    <row r="240" spans="2:27">
       <c r="B240" s="54" t="s">
         <v>64</v>
       </c>
@@ -19061,7 +19060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="2:28" hidden="1">
+    <row r="241" spans="2:28">
       <c r="B241" s="54" t="s">
         <v>64</v>
       </c>
@@ -19117,7 +19116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="2:28" hidden="1">
+    <row r="242" spans="2:28">
       <c r="B242" s="54" t="s">
         <v>64</v>
       </c>
@@ -19173,7 +19172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="2:28" hidden="1">
+    <row r="243" spans="2:28">
       <c r="B243" s="54" t="s">
         <v>64</v>
       </c>
@@ -19229,7 +19228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="2:28" hidden="1">
+    <row r="244" spans="2:28">
       <c r="B244" s="54" t="s">
         <v>64</v>
       </c>
@@ -19285,7 +19284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="2:28" hidden="1">
+    <row r="245" spans="2:28">
       <c r="B245" s="54" t="s">
         <v>64</v>
       </c>
@@ -19341,7 +19340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="2:28" hidden="1">
+    <row r="246" spans="2:28">
       <c r="B246" s="54" t="s">
         <v>64</v>
       </c>
@@ -19400,7 +19399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="2:28" hidden="1">
+    <row r="247" spans="2:28">
       <c r="B247" s="54" t="s">
         <v>64</v>
       </c>
@@ -19456,7 +19455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="2:28" hidden="1">
+    <row r="248" spans="2:28">
       <c r="B248" s="54" t="s">
         <v>64</v>
       </c>
@@ -19515,7 +19514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="2:28" hidden="1">
+    <row r="249" spans="2:28">
       <c r="B249" s="54" t="s">
         <v>64</v>
       </c>
@@ -19571,7 +19570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="2:28" hidden="1">
+    <row r="250" spans="2:28">
       <c r="B250" s="54" t="s">
         <v>64</v>
       </c>
@@ -19627,7 +19626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="2:28" hidden="1">
+    <row r="251" spans="2:28">
       <c r="B251" s="54" t="s">
         <v>64</v>
       </c>
@@ -19701,7 +19700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="2:28" hidden="1">
+    <row r="252" spans="2:28">
       <c r="B252" s="54" t="s">
         <v>64</v>
       </c>
@@ -19763,7 +19762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="2:28" hidden="1">
+    <row r="253" spans="2:28">
       <c r="B253" s="54" t="s">
         <v>64</v>
       </c>
@@ -19822,7 +19821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="2:28" hidden="1">
+    <row r="254" spans="2:28">
       <c r="B254" s="54" t="s">
         <v>64</v>
       </c>
@@ -19884,7 +19883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="2:28" hidden="1">
+    <row r="255" spans="2:28">
       <c r="B255" s="54" t="s">
         <v>64</v>
       </c>
@@ -19946,7 +19945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="2:28" hidden="1">
+    <row r="256" spans="2:28">
       <c r="B256" s="54" t="s">
         <v>64</v>
       </c>
@@ -20005,7 +20004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="2:30" hidden="1">
+    <row r="257" spans="2:30">
       <c r="B257" s="54" t="s">
         <v>64</v>
       </c>
@@ -20079,7 +20078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="2:30" hidden="1">
+    <row r="258" spans="2:30">
       <c r="B258" s="54" t="s">
         <v>64</v>
       </c>
@@ -20150,7 +20149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="2:30" hidden="1">
+    <row r="259" spans="2:30">
       <c r="B259" s="54" t="s">
         <v>64</v>
       </c>
@@ -20227,7 +20226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="2:30" hidden="1">
+    <row r="260" spans="2:30">
       <c r="B260" s="54" t="s">
         <v>64</v>
       </c>
@@ -20289,7 +20288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="2:30" hidden="1">
+    <row r="261" spans="2:30">
       <c r="B261" s="54" t="s">
         <v>64</v>
       </c>
@@ -20351,7 +20350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="2:30" hidden="1">
+    <row r="262" spans="2:30">
       <c r="B262" s="54" t="s">
         <v>64</v>
       </c>
@@ -20410,7 +20409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="2:30" hidden="1">
+    <row r="263" spans="2:30">
       <c r="B263" s="54" t="s">
         <v>64</v>
       </c>
@@ -20525,7 +20524,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="265" spans="2:30" hidden="1">
+    <row r="265" spans="2:30">
       <c r="B265" s="54" t="s">
         <v>64</v>
       </c>
@@ -20581,7 +20580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="2:30" hidden="1">
+    <row r="266" spans="2:30">
       <c r="B266" s="54" t="s">
         <v>64</v>
       </c>
@@ -20637,7 +20636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="2:30" hidden="1">
+    <row r="267" spans="2:30">
       <c r="B267" s="54" t="s">
         <v>64</v>
       </c>
@@ -20705,7 +20704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="2:30" hidden="1">
+    <row r="268" spans="2:30">
       <c r="B268" s="54" t="s">
         <v>64</v>
       </c>
@@ -20761,7 +20760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="2:30" hidden="1">
+    <row r="269" spans="2:30">
       <c r="B269" s="54" t="s">
         <v>64</v>
       </c>
@@ -20817,7 +20816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="270" spans="2:30" hidden="1">
+    <row r="270" spans="2:30">
       <c r="B270" s="54" t="s">
         <v>64</v>
       </c>
@@ -20873,7 +20872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="2:30" hidden="1">
+    <row r="271" spans="2:30">
       <c r="B271" s="54" t="s">
         <v>64</v>
       </c>
@@ -20985,7 +20984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="2:27" hidden="1">
+    <row r="273" spans="2:27">
       <c r="B273" s="54" t="s">
         <v>64</v>
       </c>
@@ -21059,7 +21058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="2:27" hidden="1">
+    <row r="274" spans="2:27">
       <c r="B274" s="54" t="s">
         <v>64</v>
       </c>
@@ -21121,7 +21120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="2:27" hidden="1">
+    <row r="275" spans="2:27">
       <c r="B275" s="54" t="s">
         <v>64</v>
       </c>
@@ -21177,7 +21176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="2:27" hidden="1">
+    <row r="276" spans="2:27">
       <c r="B276" s="54" t="s">
         <v>64</v>
       </c>
@@ -21242,7 +21241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="2:27" hidden="1">
+    <row r="277" spans="2:27">
       <c r="B277" s="54" t="s">
         <v>64</v>
       </c>
@@ -21298,7 +21297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="2:27" hidden="1">
+    <row r="278" spans="2:27">
       <c r="B278" s="54" t="s">
         <v>64</v>
       </c>
@@ -21354,7 +21353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="2:27" hidden="1">
+    <row r="279" spans="2:27">
       <c r="B279" s="54" t="s">
         <v>64</v>
       </c>
@@ -21410,7 +21409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="2:27" hidden="1">
+    <row r="280" spans="2:27">
       <c r="B280" s="54" t="s">
         <v>64</v>
       </c>
@@ -21522,7 +21521,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="282" spans="2:27" hidden="1">
+    <row r="282" spans="2:27">
       <c r="B282" s="54" t="s">
         <v>64</v>
       </c>
@@ -21578,7 +21577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="2:27" hidden="1">
+    <row r="283" spans="2:27">
       <c r="B283" s="54" t="s">
         <v>64</v>
       </c>
@@ -21634,7 +21633,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="284" spans="2:27" hidden="1">
+    <row r="284" spans="2:27">
       <c r="B284" s="54" t="s">
         <v>64</v>
       </c>
@@ -21690,7 +21689,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="285" spans="2:27" hidden="1">
+    <row r="285" spans="2:27">
       <c r="B285" s="54" t="s">
         <v>64</v>
       </c>
@@ -21755,7 +21754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="2:27" hidden="1">
+    <row r="286" spans="2:27">
       <c r="B286" s="54" t="s">
         <v>64</v>
       </c>
@@ -21811,7 +21810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="287" spans="2:27" hidden="1">
+    <row r="287" spans="2:27">
       <c r="B287" s="54" t="s">
         <v>64</v>
       </c>
@@ -21867,7 +21866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="288" spans="2:27" hidden="1">
+    <row r="288" spans="2:27">
       <c r="B288" s="54" t="s">
         <v>64</v>
       </c>
@@ -21923,7 +21922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="2:40" hidden="1">
+    <row r="289" spans="2:40">
       <c r="B289" s="54" t="s">
         <v>64</v>
       </c>
@@ -21982,7 +21981,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="290" spans="2:40" hidden="1">
+    <row r="290" spans="2:40">
       <c r="B290" s="54" t="s">
         <v>64</v>
       </c>
@@ -22038,7 +22037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="291" spans="2:40" hidden="1">
+    <row r="291" spans="2:40">
       <c r="B291" s="54" t="s">
         <v>64</v>
       </c>
@@ -22156,7 +22155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="293" spans="2:40" hidden="1">
+    <row r="293" spans="2:40">
       <c r="B293" s="54" t="s">
         <v>64</v>
       </c>
@@ -22212,7 +22211,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="294" spans="2:40" hidden="1">
+    <row r="294" spans="2:40">
       <c r="B294" s="54" t="s">
         <v>64</v>
       </c>
@@ -22268,7 +22267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="2:40" hidden="1">
+    <row r="295" spans="2:40">
       <c r="B295" s="54" t="s">
         <v>64</v>
       </c>
@@ -22324,7 +22323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="2:40" hidden="1">
+    <row r="296" spans="2:40">
       <c r="B296" s="54" t="s">
         <v>64</v>
       </c>
@@ -22383,7 +22382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="2:40" hidden="1">
+    <row r="297" spans="2:40">
       <c r="B297" s="54" t="s">
         <v>64</v>
       </c>
@@ -22442,7 +22441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="2:40" hidden="1">
+    <row r="298" spans="2:40">
       <c r="B298" s="54" t="s">
         <v>64</v>
       </c>
@@ -22501,7 +22500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="2:40" hidden="1">
+    <row r="299" spans="2:40">
       <c r="B299" s="54" t="s">
         <v>64</v>
       </c>
@@ -22560,7 +22559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="2:40" hidden="1">
+    <row r="300" spans="2:40">
       <c r="B300" s="54" t="s">
         <v>64</v>
       </c>
@@ -22619,7 +22618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="2:40" hidden="1">
+    <row r="301" spans="2:40">
       <c r="B301" s="54" t="s">
         <v>64</v>
       </c>
@@ -22678,7 +22677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="2:40" hidden="1">
+    <row r="302" spans="2:40">
       <c r="B302" s="54" t="s">
         <v>64</v>
       </c>
@@ -22740,7 +22739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="2:40" hidden="1">
+    <row r="303" spans="2:40">
       <c r="B303" s="54" t="s">
         <v>64</v>
       </c>
@@ -22808,7 +22807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="2:40" hidden="1">
+    <row r="304" spans="2:40">
       <c r="B304" s="54" t="s">
         <v>64</v>
       </c>
@@ -22873,7 +22872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="2:26" hidden="1">
+    <row r="305" spans="2:26">
       <c r="B305" s="54" t="s">
         <v>64</v>
       </c>
@@ -22932,7 +22931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="2:26" hidden="1">
+    <row r="306" spans="2:26">
       <c r="B306" s="54" t="s">
         <v>64</v>
       </c>
@@ -22988,7 +22987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="2:26" hidden="1">
+    <row r="307" spans="2:26">
       <c r="B307" s="54" t="s">
         <v>64</v>
       </c>
@@ -23062,7 +23061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="2:26" hidden="1">
+    <row r="308" spans="2:26">
       <c r="B308" s="54" t="s">
         <v>64</v>
       </c>
@@ -23174,7 +23173,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="310" spans="2:26" hidden="1">
+    <row r="310" spans="2:26">
       <c r="B310" s="54" t="s">
         <v>64</v>
       </c>
@@ -23230,7 +23229,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="311" spans="2:26" hidden="1">
+    <row r="311" spans="2:26">
       <c r="B311" s="54" t="s">
         <v>64</v>
       </c>
@@ -23286,7 +23285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="2:26" hidden="1">
+    <row r="312" spans="2:26">
       <c r="B312" s="54" t="s">
         <v>64</v>
       </c>
@@ -23342,7 +23341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="2:26" hidden="1">
+    <row r="313" spans="2:26">
       <c r="B313" s="54" t="s">
         <v>64</v>
       </c>
@@ -23398,7 +23397,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="2:26" hidden="1">
+    <row r="314" spans="2:26">
       <c r="B314" s="54" t="s">
         <v>64</v>
       </c>
@@ -23454,7 +23453,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="315" spans="2:26" hidden="1">
+    <row r="315" spans="2:26">
       <c r="B315" s="54" t="s">
         <v>64</v>
       </c>
@@ -23513,7 +23512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="2:26" hidden="1">
+    <row r="316" spans="2:26">
       <c r="B316" s="54" t="s">
         <v>64</v>
       </c>
@@ -23575,7 +23574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="2:26" hidden="1">
+    <row r="317" spans="2:26">
       <c r="B317" s="54" t="s">
         <v>64</v>
       </c>
@@ -23631,7 +23630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="2:26" hidden="1">
+    <row r="318" spans="2:26">
       <c r="B318" s="54" t="s">
         <v>64</v>
       </c>
@@ -23743,7 +23742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="320" spans="2:26" hidden="1">
+    <row r="320" spans="2:26">
       <c r="B320" s="54" t="s">
         <v>64</v>
       </c>
@@ -23799,7 +23798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="321" spans="2:28" hidden="1">
+    <row r="321" spans="2:28">
       <c r="B321" s="54" t="s">
         <v>64</v>
       </c>
@@ -23858,7 +23857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="2:28" hidden="1">
+    <row r="322" spans="2:28">
       <c r="B322" s="54" t="s">
         <v>64</v>
       </c>
@@ -23914,7 +23913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="2:28" hidden="1">
+    <row r="323" spans="2:28">
       <c r="B323" s="54" t="s">
         <v>64</v>
       </c>
@@ -23973,7 +23972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="2:28" hidden="1">
+    <row r="324" spans="2:28">
       <c r="B324" s="54" t="s">
         <v>64</v>
       </c>
@@ -24029,7 +24028,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:28" hidden="1">
+    <row r="325" spans="2:28">
       <c r="B325" s="54" t="s">
         <v>64</v>
       </c>
@@ -24103,7 +24102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="326" spans="2:28" hidden="1">
+    <row r="326" spans="2:28">
       <c r="B326" s="54" t="s">
         <v>64</v>
       </c>
@@ -24159,7 +24158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="2:28" hidden="1">
+    <row r="327" spans="2:28">
       <c r="B327" s="54" t="s">
         <v>64</v>
       </c>
@@ -24215,7 +24214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="2:28" hidden="1">
+    <row r="328" spans="2:28">
       <c r="B328" s="54" t="s">
         <v>64</v>
       </c>
@@ -24383,7 +24382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="2:28" hidden="1">
+    <row r="331" spans="2:28">
       <c r="B331" s="54" t="s">
         <v>64</v>
       </c>
@@ -24439,7 +24438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="2:28" hidden="1">
+    <row r="332" spans="2:28">
       <c r="B332" s="54" t="s">
         <v>64</v>
       </c>
@@ -24495,7 +24494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="333" spans="2:28" hidden="1">
+    <row r="333" spans="2:28">
       <c r="B333" s="54" t="s">
         <v>64</v>
       </c>
@@ -24551,7 +24550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="2:28" hidden="1">
+    <row r="334" spans="2:28">
       <c r="B334" s="54" t="s">
         <v>64</v>
       </c>
@@ -24610,7 +24609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="2:28" hidden="1">
+    <row r="335" spans="2:28">
       <c r="B335" s="54" t="s">
         <v>64</v>
       </c>
@@ -24666,7 +24665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="2:28" hidden="1">
+    <row r="336" spans="2:28">
       <c r="B336" s="54" t="s">
         <v>64</v>
       </c>
@@ -24722,7 +24721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="2:31" hidden="1">
+    <row r="337" spans="2:31">
       <c r="B337" s="54" t="s">
         <v>64</v>
       </c>
@@ -24784,7 +24783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="2:31" hidden="1">
+    <row r="338" spans="2:31">
       <c r="B338" s="54" t="s">
         <v>64</v>
       </c>
@@ -24840,7 +24839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="2:31" hidden="1">
+    <row r="339" spans="2:31">
       <c r="B339" s="54" t="s">
         <v>64</v>
       </c>
@@ -24896,7 +24895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="2:31" hidden="1">
+    <row r="340" spans="2:31">
       <c r="B340" s="54" t="s">
         <v>64</v>
       </c>
@@ -24958,7 +24957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="2:31" hidden="1">
+    <row r="341" spans="2:31">
       <c r="B341" s="54" t="s">
         <v>64</v>
       </c>
@@ -25014,7 +25013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="2:31" hidden="1">
+    <row r="342" spans="2:31">
       <c r="B342" s="54" t="s">
         <v>64</v>
       </c>
@@ -25070,7 +25069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="2:31" hidden="1">
+    <row r="343" spans="2:31">
       <c r="B343" s="54" t="s">
         <v>64</v>
       </c>
@@ -25129,7 +25128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="2:31" hidden="1">
+    <row r="344" spans="2:31">
       <c r="B344" s="54" t="s">
         <v>64</v>
       </c>
@@ -25188,7 +25187,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="2:31" hidden="1">
+    <row r="345" spans="2:31">
       <c r="B345" s="54" t="s">
         <v>64</v>
       </c>
@@ -25256,7 +25255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="2:31" hidden="1">
+    <row r="346" spans="2:31">
       <c r="B346" s="54" t="s">
         <v>64</v>
       </c>
@@ -25315,7 +25314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="2:31" hidden="1">
+    <row r="347" spans="2:31">
       <c r="B347" s="54" t="s">
         <v>64</v>
       </c>
@@ -25374,7 +25373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="2:31" hidden="1">
+    <row r="348" spans="2:31">
       <c r="B348" s="54" t="s">
         <v>64</v>
       </c>
@@ -25433,7 +25432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="2:31" hidden="1">
+    <row r="349" spans="2:31">
       <c r="B349" s="54" t="s">
         <v>64</v>
       </c>
@@ -25557,7 +25556,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="351" spans="2:31" hidden="1">
+    <row r="351" spans="2:31">
       <c r="B351" s="54" t="s">
         <v>64</v>
       </c>
@@ -25613,7 +25612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="2:31" hidden="1">
+    <row r="352" spans="2:31">
       <c r="B352" s="54" t="s">
         <v>64</v>
       </c>
@@ -25669,7 +25668,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="353" spans="2:33" hidden="1">
+    <row r="353" spans="2:33">
       <c r="B353" s="54" t="s">
         <v>64</v>
       </c>
@@ -25725,7 +25724,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="354" spans="2:33" hidden="1">
+    <row r="354" spans="2:33">
       <c r="B354" s="54" t="s">
         <v>64</v>
       </c>
@@ -25837,7 +25836,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="356" spans="2:33" hidden="1">
+    <row r="356" spans="2:33">
       <c r="B356" s="54" t="s">
         <v>64</v>
       </c>
@@ -25893,7 +25892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="2:33" hidden="1">
+    <row r="357" spans="2:33">
       <c r="B357" s="54" t="s">
         <v>64</v>
       </c>
@@ -25949,7 +25948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="358" spans="2:33" hidden="1">
+    <row r="358" spans="2:33">
       <c r="B358" s="54" t="s">
         <v>64</v>
       </c>
@@ -26005,7 +26004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="359" spans="2:33" hidden="1">
+    <row r="359" spans="2:33">
       <c r="B359" s="54" t="s">
         <v>64</v>
       </c>
@@ -26061,7 +26060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="2:33" hidden="1">
+    <row r="360" spans="2:33">
       <c r="B360" s="54" t="s">
         <v>64</v>
       </c>
@@ -26120,7 +26119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="2:33" hidden="1">
+    <row r="361" spans="2:33">
       <c r="B361" s="54" t="s">
         <v>64</v>
       </c>
@@ -26182,7 +26181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="2:33" hidden="1">
+    <row r="362" spans="2:33">
       <c r="B362" s="54" t="s">
         <v>64</v>
       </c>
@@ -26238,7 +26237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="2:33" hidden="1">
+    <row r="363" spans="2:33">
       <c r="B363" s="54" t="s">
         <v>64</v>
       </c>
@@ -26297,7 +26296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="2:33" hidden="1">
+    <row r="364" spans="2:33">
       <c r="B364" s="54" t="s">
         <v>64</v>
       </c>
@@ -26412,7 +26411,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="366" spans="2:33" hidden="1">
+    <row r="366" spans="2:33">
       <c r="B366" s="54" t="s">
         <v>64</v>
       </c>
@@ -26468,7 +26467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="2:33" hidden="1">
+    <row r="367" spans="2:33">
       <c r="B367" s="54" t="s">
         <v>64</v>
       </c>
@@ -26583,7 +26582,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="369" spans="2:29" hidden="1">
+    <row r="369" spans="2:29">
       <c r="B369" s="54" t="s">
         <v>64</v>
       </c>
@@ -26651,7 +26650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="2:29" hidden="1">
+    <row r="370" spans="2:29">
       <c r="B370" s="54" t="s">
         <v>64</v>
       </c>
@@ -26707,7 +26706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="371" spans="2:29" hidden="1">
+    <row r="371" spans="2:29">
       <c r="B371" s="54" t="s">
         <v>64</v>
       </c>
@@ -26763,7 +26762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="372" spans="2:29" hidden="1">
+    <row r="372" spans="2:29">
       <c r="B372" s="54" t="s">
         <v>64</v>
       </c>
@@ -26819,7 +26818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="373" spans="2:29" hidden="1">
+    <row r="373" spans="2:29">
       <c r="B373" s="54" t="s">
         <v>64</v>
       </c>
@@ -26875,7 +26874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="2:29" hidden="1">
+    <row r="374" spans="2:29">
       <c r="B374" s="54" t="s">
         <v>64</v>
       </c>
@@ -26931,7 +26930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="375" spans="2:29" hidden="1">
+    <row r="375" spans="2:29">
       <c r="B375" s="54" t="s">
         <v>64</v>
       </c>
@@ -26990,7 +26989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="376" spans="2:29" hidden="1">
+    <row r="376" spans="2:29">
       <c r="B376" s="54" t="s">
         <v>64</v>
       </c>
@@ -27046,7 +27045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="2:29" hidden="1">
+    <row r="377" spans="2:29">
       <c r="B377" s="54" t="s">
         <v>64</v>
       </c>
@@ -27102,7 +27101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="2:29" hidden="1">
+    <row r="378" spans="2:29">
       <c r="B378" s="54" t="s">
         <v>64</v>
       </c>
@@ -27158,7 +27157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="2:29" hidden="1">
+    <row r="379" spans="2:29">
       <c r="B379" s="54" t="s">
         <v>64</v>
       </c>
@@ -27217,7 +27216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="2:29" hidden="1">
+    <row r="380" spans="2:29">
       <c r="B380" s="54" t="s">
         <v>64</v>
       </c>
@@ -27276,7 +27275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="2:29" hidden="1">
+    <row r="381" spans="2:29">
       <c r="B381" s="54" t="s">
         <v>64</v>
       </c>
@@ -27344,7 +27343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="2:29" hidden="1">
+    <row r="382" spans="2:29">
       <c r="B382" s="54" t="s">
         <v>64</v>
       </c>
@@ -27403,7 +27402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="2:29" hidden="1">
+    <row r="383" spans="2:29">
       <c r="B383" s="54" t="s">
         <v>64</v>
       </c>
@@ -27465,7 +27464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="2:29" hidden="1">
+    <row r="384" spans="2:29">
       <c r="B384" s="54" t="s">
         <v>64</v>
       </c>
@@ -27536,7 +27535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="385" spans="2:28" hidden="1">
+    <row r="385" spans="2:28">
       <c r="B385" s="54" t="s">
         <v>64</v>
       </c>
@@ -27595,7 +27594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="2:28" hidden="1">
+    <row r="386" spans="2:28">
       <c r="B386" s="54" t="s">
         <v>64</v>
       </c>
@@ -27654,7 +27653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="2:28" hidden="1">
+    <row r="387" spans="2:28">
       <c r="B387" s="54" t="s">
         <v>64</v>
       </c>
@@ -27713,7 +27712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="2:28" hidden="1">
+    <row r="388" spans="2:28">
       <c r="B388" s="54" t="s">
         <v>64</v>
       </c>
@@ -27775,7 +27774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="2:28" hidden="1">
+    <row r="389" spans="2:28">
       <c r="B389" s="54" t="s">
         <v>64</v>
       </c>
@@ -27834,7 +27833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="2:28" hidden="1">
+    <row r="390" spans="2:28">
       <c r="B390" s="54" t="s">
         <v>64</v>
       </c>
@@ -27905,7 +27904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="2:28" hidden="1">
+    <row r="391" spans="2:28">
       <c r="B391" s="54" t="s">
         <v>64</v>
       </c>
@@ -27967,7 +27966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="2:28" hidden="1">
+    <row r="392" spans="2:28">
       <c r="B392" s="54" t="s">
         <v>64</v>
       </c>
@@ -28085,7 +28084,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="394" spans="2:28" hidden="1">
+    <row r="394" spans="2:28">
       <c r="B394" s="54" t="s">
         <v>64</v>
       </c>
@@ -28141,7 +28140,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="395" spans="2:28" hidden="1">
+    <row r="395" spans="2:28">
       <c r="B395" s="54" t="s">
         <v>64</v>
       </c>
@@ -28197,7 +28196,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="396" spans="2:28" hidden="1">
+    <row r="396" spans="2:28">
       <c r="B396" s="54" t="s">
         <v>64</v>
       </c>
@@ -28274,7 +28273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="2:28" hidden="1">
+    <row r="397" spans="2:28">
       <c r="B397" s="54" t="s">
         <v>64</v>
       </c>
@@ -28330,7 +28329,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="398" spans="2:28" hidden="1">
+    <row r="398" spans="2:28">
       <c r="B398" s="54" t="s">
         <v>64</v>
       </c>
@@ -28389,7 +28388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="2:28" hidden="1">
+    <row r="399" spans="2:28">
       <c r="B399" s="54" t="s">
         <v>64</v>
       </c>
@@ -28445,7 +28444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="400" spans="2:28" hidden="1">
+    <row r="400" spans="2:28">
       <c r="B400" s="54" t="s">
         <v>64</v>
       </c>
@@ -28519,7 +28518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="2:25" hidden="1">
+    <row r="401" spans="2:25">
       <c r="B401" s="54" t="s">
         <v>64</v>
       </c>
@@ -28575,7 +28574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="2:25" hidden="1">
+    <row r="402" spans="2:25">
       <c r="B402" s="54" t="s">
         <v>64</v>
       </c>
@@ -28631,7 +28630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="2:25" hidden="1">
+    <row r="403" spans="2:25">
       <c r="B403" s="54" t="s">
         <v>64</v>
       </c>
@@ -28687,7 +28686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="404" spans="2:25" hidden="1">
+    <row r="404" spans="2:25">
       <c r="B404" s="54" t="s">
         <v>64</v>
       </c>
@@ -28743,7 +28742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="2:25" hidden="1">
+    <row r="405" spans="2:25">
       <c r="B405" s="54" t="s">
         <v>64</v>
       </c>
@@ -28808,7 +28807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="2:25" hidden="1">
+    <row r="406" spans="2:25">
       <c r="B406" s="54" t="s">
         <v>64</v>
       </c>
@@ -28920,7 +28919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="2:25" hidden="1">
+    <row r="408" spans="2:25">
       <c r="B408" s="54" t="s">
         <v>64</v>
       </c>
@@ -28976,7 +28975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="2:25" hidden="1">
+    <row r="409" spans="2:25">
       <c r="B409" s="54" t="s">
         <v>64</v>
       </c>
@@ -29032,7 +29031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="2:25" hidden="1">
+    <row r="410" spans="2:25">
       <c r="B410" s="54" t="s">
         <v>64</v>
       </c>
@@ -29088,7 +29087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="2:25" hidden="1">
+    <row r="411" spans="2:25">
       <c r="B411" s="54" t="s">
         <v>64</v>
       </c>
@@ -29144,7 +29143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="2:25" hidden="1">
+    <row r="412" spans="2:25">
       <c r="B412" s="54" t="s">
         <v>64</v>
       </c>
@@ -29200,7 +29199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="2:25" hidden="1">
+    <row r="413" spans="2:25">
       <c r="B413" s="54" t="s">
         <v>64</v>
       </c>
@@ -29256,7 +29255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="2:25" hidden="1">
+    <row r="414" spans="2:25">
       <c r="B414" s="54" t="s">
         <v>64</v>
       </c>
@@ -29312,7 +29311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="2:25" hidden="1">
+    <row r="415" spans="2:25">
       <c r="B415" s="54" t="s">
         <v>64</v>
       </c>
@@ -29368,7 +29367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="2:25" hidden="1">
+    <row r="416" spans="2:25">
       <c r="B416" s="54" t="s">
         <v>64</v>
       </c>
@@ -29424,7 +29423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="2:26" hidden="1">
+    <row r="417" spans="2:26">
       <c r="B417" s="54" t="s">
         <v>64</v>
       </c>
@@ -29480,7 +29479,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="418" spans="2:26" hidden="1">
+    <row r="418" spans="2:26">
       <c r="B418" s="54" t="s">
         <v>64</v>
       </c>
@@ -29545,7 +29544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="419" spans="2:26" hidden="1">
+    <row r="419" spans="2:26">
       <c r="B419" s="54" t="s">
         <v>64</v>
       </c>
@@ -29613,7 +29612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="2:26" hidden="1">
+    <row r="420" spans="2:26">
       <c r="B420" s="54" t="s">
         <v>64</v>
       </c>
@@ -29669,7 +29668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="421" spans="2:26" hidden="1">
+    <row r="421" spans="2:26">
       <c r="B421" s="54" t="s">
         <v>64</v>
       </c>
@@ -29725,7 +29724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="422" spans="2:26" hidden="1">
+    <row r="422" spans="2:26">
       <c r="B422" s="54" t="s">
         <v>64</v>
       </c>
@@ -29852,7 +29851,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="424" spans="2:26" hidden="1">
+    <row r="424" spans="2:26">
       <c r="B424" s="54" t="s">
         <v>64</v>
       </c>
@@ -29908,7 +29907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="2:26" hidden="1">
+    <row r="425" spans="2:26">
       <c r="B425" s="54" t="s">
         <v>64</v>
       </c>
@@ -29964,7 +29963,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="2:26" hidden="1">
+    <row r="426" spans="2:26">
       <c r="B426" s="54" t="s">
         <v>64</v>
       </c>
@@ -30020,7 +30019,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="427" spans="2:26" hidden="1">
+    <row r="427" spans="2:26">
       <c r="B427" s="54" t="s">
         <v>64</v>
       </c>
@@ -30076,7 +30075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="2:26" hidden="1">
+    <row r="428" spans="2:26">
       <c r="B428" s="54" t="s">
         <v>64</v>
       </c>
@@ -30132,7 +30131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="2:26" hidden="1">
+    <row r="429" spans="2:26">
       <c r="B429" s="54" t="s">
         <v>64</v>
       </c>
@@ -30188,7 +30187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="2:26" hidden="1">
+    <row r="430" spans="2:26">
       <c r="B430" s="54" t="s">
         <v>64</v>
       </c>
@@ -30244,7 +30243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="2:26" hidden="1">
+    <row r="431" spans="2:26">
       <c r="B431" s="54" t="s">
         <v>64</v>
       </c>
@@ -30300,7 +30299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="2:26" hidden="1">
+    <row r="432" spans="2:26">
       <c r="B432" s="54" t="s">
         <v>64</v>
       </c>
@@ -30356,7 +30355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="2:29" hidden="1">
+    <row r="433" spans="2:29">
       <c r="B433" s="54" t="s">
         <v>64</v>
       </c>
@@ -30412,7 +30411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="2:29" hidden="1">
+    <row r="434" spans="2:29">
       <c r="B434" s="54" t="s">
         <v>64</v>
       </c>
@@ -30468,7 +30467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="2:29" hidden="1">
+    <row r="435" spans="2:29">
       <c r="B435" s="54" t="s">
         <v>64</v>
       </c>
@@ -30524,7 +30523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="2:29" hidden="1">
+    <row r="436" spans="2:29">
       <c r="B436" s="54" t="s">
         <v>64</v>
       </c>
@@ -30583,7 +30582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="2:29" hidden="1">
+    <row r="437" spans="2:29">
       <c r="B437" s="54" t="s">
         <v>64</v>
       </c>
@@ -30645,7 +30644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="438" spans="2:29" hidden="1">
+    <row r="438" spans="2:29">
       <c r="B438" s="54" t="s">
         <v>64</v>
       </c>
@@ -30704,7 +30703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="2:29" hidden="1">
+    <row r="439" spans="2:29">
       <c r="B439" s="54" t="s">
         <v>64</v>
       </c>
@@ -30763,7 +30762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="2:29" hidden="1">
+    <row r="440" spans="2:29">
       <c r="B440" s="54" t="s">
         <v>64</v>
       </c>
@@ -30831,7 +30830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="2:29" hidden="1">
+    <row r="441" spans="2:29">
       <c r="B441" s="54" t="s">
         <v>64</v>
       </c>
@@ -30902,7 +30901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="2:29" hidden="1">
+    <row r="442" spans="2:29">
       <c r="B442" s="54" t="s">
         <v>64</v>
       </c>
@@ -30967,7 +30966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="2:29" hidden="1">
+    <row r="443" spans="2:29">
       <c r="B443" s="54" t="s">
         <v>64</v>
       </c>
@@ -31032,7 +31031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="2:29" hidden="1">
+    <row r="444" spans="2:29">
       <c r="B444" s="54" t="s">
         <v>64</v>
       </c>
@@ -31100,7 +31099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="445" spans="2:29" hidden="1">
+    <row r="445" spans="2:29">
       <c r="B445" s="54" t="s">
         <v>64</v>
       </c>
@@ -31221,7 +31220,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="447" spans="2:29" hidden="1">
+    <row r="447" spans="2:29">
       <c r="B447" s="54" t="s">
         <v>64</v>
       </c>
@@ -31277,7 +31276,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="448" spans="2:29" hidden="1">
+    <row r="448" spans="2:29">
       <c r="B448" s="54" t="s">
         <v>64</v>
       </c>
@@ -31333,7 +31332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="2:26" hidden="1">
+    <row r="449" spans="2:26">
       <c r="B449" s="54" t="s">
         <v>64</v>
       </c>
@@ -31389,7 +31388,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="450" spans="2:26" hidden="1">
+    <row r="450" spans="2:26">
       <c r="B450" s="54" t="s">
         <v>64</v>
       </c>
@@ -31445,7 +31444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="2:26" hidden="1">
+    <row r="451" spans="2:26">
       <c r="B451" s="54" t="s">
         <v>64</v>
       </c>
@@ -31501,7 +31500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="2:26" hidden="1">
+    <row r="452" spans="2:26">
       <c r="B452" s="54" t="s">
         <v>64</v>
       </c>
@@ -31575,7 +31574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="453" spans="2:26" hidden="1">
+    <row r="453" spans="2:26">
       <c r="B453" s="54" t="s">
         <v>64</v>
       </c>
@@ -31631,7 +31630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="2:26" hidden="1">
+    <row r="454" spans="2:26">
       <c r="B454" s="54" t="s">
         <v>64</v>
       </c>
@@ -31690,7 +31689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="2:26" hidden="1">
+    <row r="455" spans="2:26">
       <c r="B455" s="54" t="s">
         <v>64</v>
       </c>
@@ -31752,7 +31751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="2:26" hidden="1">
+    <row r="456" spans="2:26">
       <c r="B456" s="54" t="s">
         <v>64</v>
       </c>
@@ -31808,7 +31807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="2:26" hidden="1">
+    <row r="457" spans="2:26">
       <c r="B457" s="54" t="s">
         <v>64</v>
       </c>
@@ -31920,7 +31919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="2:26" hidden="1">
+    <row r="459" spans="2:26">
       <c r="B459" s="54" t="s">
         <v>64</v>
       </c>
@@ -31976,7 +31975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="2:26" hidden="1">
+    <row r="460" spans="2:26">
       <c r="B460" s="54" t="s">
         <v>64</v>
       </c>
@@ -32032,7 +32031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="2:26" hidden="1">
+    <row r="461" spans="2:26">
       <c r="B461" s="54" t="s">
         <v>64</v>
       </c>
@@ -32088,7 +32087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="2:26" hidden="1">
+    <row r="462" spans="2:26">
       <c r="B462" s="54" t="s">
         <v>64</v>
       </c>
@@ -32147,7 +32146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="2:26" hidden="1">
+    <row r="463" spans="2:26">
       <c r="B463" s="54" t="s">
         <v>64</v>
       </c>
@@ -32203,7 +32202,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="464" spans="2:26" hidden="1">
+    <row r="464" spans="2:26">
       <c r="B464" s="54" t="s">
         <v>64</v>
       </c>
@@ -32274,7 +32273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="2:26" hidden="1">
+    <row r="465" spans="2:26">
       <c r="B465" s="54" t="s">
         <v>64</v>
       </c>
@@ -32330,7 +32329,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="466" spans="2:26" hidden="1">
+    <row r="466" spans="2:26">
       <c r="B466" s="54" t="s">
         <v>64</v>
       </c>
@@ -32442,7 +32441,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="468" spans="2:26" hidden="1">
+    <row r="468" spans="2:26">
       <c r="B468" s="54" t="s">
         <v>64</v>
       </c>
@@ -32498,7 +32497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="2:26" hidden="1">
+    <row r="469" spans="2:26">
       <c r="B469" s="54" t="s">
         <v>64</v>
       </c>
@@ -32554,7 +32553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="2:26" hidden="1">
+    <row r="470" spans="2:26">
       <c r="B470" s="54" t="s">
         <v>64</v>
       </c>
@@ -32610,7 +32609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="2:26" hidden="1">
+    <row r="471" spans="2:26">
       <c r="B471" s="54" t="s">
         <v>64</v>
       </c>
@@ -32666,7 +32665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="2:26" hidden="1">
+    <row r="472" spans="2:26">
       <c r="B472" s="54" t="s">
         <v>64</v>
       </c>
@@ -32778,7 +32777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="474" spans="2:26" hidden="1">
+    <row r="474" spans="2:26">
       <c r="B474" s="54" t="s">
         <v>64</v>
       </c>
@@ -32834,7 +32833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="2:26" hidden="1">
+    <row r="475" spans="2:26">
       <c r="B475" s="54" t="s">
         <v>64</v>
       </c>
@@ -32890,7 +32889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="2:26" hidden="1">
+    <row r="476" spans="2:26">
       <c r="B476" s="54" t="s">
         <v>64</v>
       </c>
@@ -32949,7 +32948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="2:26" hidden="1">
+    <row r="477" spans="2:26">
       <c r="B477" s="54" t="s">
         <v>64</v>
       </c>
@@ -33005,7 +33004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="2:26" hidden="1">
+    <row r="478" spans="2:26">
       <c r="B478" s="54" t="s">
         <v>64</v>
       </c>
@@ -33061,7 +33060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="2:26" hidden="1">
+    <row r="479" spans="2:26">
       <c r="B479" s="54" t="s">
         <v>64</v>
       </c>
@@ -33117,7 +33116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="2:26" hidden="1">
+    <row r="480" spans="2:26">
       <c r="B480" s="54" t="s">
         <v>64</v>
       </c>
@@ -33176,7 +33175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="2:28" hidden="1">
+    <row r="481" spans="2:28">
       <c r="B481" s="54" t="s">
         <v>64</v>
       </c>
@@ -33235,7 +33234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="2:28" hidden="1">
+    <row r="482" spans="2:28">
       <c r="B482" s="54" t="s">
         <v>64</v>
       </c>
@@ -33294,7 +33293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="2:28" hidden="1">
+    <row r="483" spans="2:28">
       <c r="B483" s="54" t="s">
         <v>64</v>
       </c>
@@ -33353,7 +33352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="484" spans="2:28" hidden="1">
+    <row r="484" spans="2:28">
       <c r="B484" s="54" t="s">
         <v>64</v>
       </c>
@@ -33412,7 +33411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="2:28" hidden="1">
+    <row r="485" spans="2:28">
       <c r="B485" s="54" t="s">
         <v>64</v>
       </c>
@@ -33471,7 +33470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="2:28" hidden="1">
+    <row r="486" spans="2:28">
       <c r="B486" s="54" t="s">
         <v>64</v>
       </c>
@@ -33533,7 +33532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="2:28" hidden="1">
+    <row r="487" spans="2:28">
       <c r="B487" s="54" t="s">
         <v>64</v>
       </c>
@@ -33589,7 +33588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="2:28" hidden="1">
+    <row r="488" spans="2:28">
       <c r="B488" s="54" t="s">
         <v>64</v>
       </c>
@@ -33648,7 +33647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="2:28" hidden="1">
+    <row r="489" spans="2:28">
       <c r="B489" s="54" t="s">
         <v>65</v>
       </c>
@@ -33707,7 +33706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="2:28" hidden="1">
+    <row r="490" spans="2:28">
       <c r="B490" s="54" t="s">
         <v>65</v>
       </c>
@@ -33825,7 +33824,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="492" spans="2:28" hidden="1">
+    <row r="492" spans="2:28">
       <c r="B492" s="54" t="s">
         <v>64</v>
       </c>
@@ -33881,7 +33880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="493" spans="2:28" hidden="1">
+    <row r="493" spans="2:28">
       <c r="B493" s="54" t="s">
         <v>64</v>
       </c>
@@ -33993,7 +33992,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="495" spans="2:28" hidden="1">
+    <row r="495" spans="2:28">
       <c r="B495" s="54" t="s">
         <v>64</v>
       </c>
@@ -34049,7 +34048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="496" spans="2:28" hidden="1">
+    <row r="496" spans="2:28">
       <c r="B496" s="54" t="s">
         <v>64</v>
       </c>
@@ -34105,7 +34104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="2:26" hidden="1">
+    <row r="497" spans="2:26">
       <c r="B497" s="54" t="s">
         <v>64</v>
       </c>
@@ -34173,7 +34172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="2:26" hidden="1">
+    <row r="498" spans="2:26">
       <c r="B498" s="54" t="s">
         <v>64</v>
       </c>
@@ -34229,7 +34228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="2:26" hidden="1">
+    <row r="499" spans="2:26">
       <c r="B499" s="54" t="s">
         <v>64</v>
       </c>
@@ -34285,7 +34284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="2:26" hidden="1">
+    <row r="500" spans="2:26">
       <c r="B500" s="54" t="s">
         <v>64</v>
       </c>
@@ -34341,7 +34340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="501" spans="2:26" hidden="1">
+    <row r="501" spans="2:26">
       <c r="B501" s="54" t="s">
         <v>64</v>
       </c>
@@ -34406,7 +34405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="502" spans="2:26" hidden="1">
+    <row r="502" spans="2:26">
       <c r="B502" s="54" t="s">
         <v>64</v>
       </c>
@@ -34462,7 +34461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="503" spans="2:26" hidden="1">
+    <row r="503" spans="2:26">
       <c r="B503" s="54" t="s">
         <v>64</v>
       </c>
@@ -34518,7 +34517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="2:26" hidden="1">
+    <row r="504" spans="2:26">
       <c r="B504" s="54" t="s">
         <v>64</v>
       </c>
@@ -34574,7 +34573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="2:26" hidden="1">
+    <row r="505" spans="2:26">
       <c r="B505" s="54" t="s">
         <v>64</v>
       </c>
@@ -34630,7 +34629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="506" spans="2:26" hidden="1">
+    <row r="506" spans="2:26">
       <c r="B506" s="54" t="s">
         <v>64</v>
       </c>
@@ -34686,7 +34685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="2:26" hidden="1">
+    <row r="507" spans="2:26">
       <c r="B507" s="54" t="s">
         <v>64</v>
       </c>
@@ -34742,7 +34741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="2:26" hidden="1">
+    <row r="508" spans="2:26">
       <c r="B508" s="54" t="s">
         <v>64</v>
       </c>
@@ -34798,7 +34797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="2:26" hidden="1">
+    <row r="509" spans="2:26">
       <c r="B509" s="54" t="s">
         <v>64</v>
       </c>
@@ -34857,7 +34856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="2:26" hidden="1">
+    <row r="510" spans="2:26">
       <c r="B510" s="54" t="s">
         <v>64</v>
       </c>
@@ -34913,7 +34912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="2:26" hidden="1">
+    <row r="511" spans="2:26">
       <c r="B511" s="54" t="s">
         <v>64</v>
       </c>
@@ -34969,7 +34968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="2:26" hidden="1">
+    <row r="512" spans="2:26">
       <c r="B512" s="54" t="s">
         <v>65</v>
       </c>
@@ -35025,7 +35024,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="513" spans="2:27" hidden="1">
+    <row r="513" spans="2:27">
       <c r="B513" s="54" t="s">
         <v>65</v>
       </c>
@@ -35096,7 +35095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="2:27" hidden="1">
+    <row r="514" spans="2:27">
       <c r="B514" s="54" t="s">
         <v>65</v>
       </c>
@@ -35158,7 +35157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="2:27" hidden="1">
+    <row r="515" spans="2:27">
       <c r="B515" s="54" t="s">
         <v>65</v>
       </c>
@@ -35270,7 +35269,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="517" spans="2:27" hidden="1">
+    <row r="517" spans="2:27">
       <c r="B517" s="54" t="s">
         <v>65</v>
       </c>
@@ -35326,7 +35325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="2:27" hidden="1">
+    <row r="518" spans="2:27">
       <c r="B518" s="54" t="s">
         <v>65</v>
       </c>
@@ -35382,7 +35381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="519" spans="2:27" hidden="1">
+    <row r="519" spans="2:27">
       <c r="B519" s="54" t="s">
         <v>65</v>
       </c>
@@ -35494,7 +35493,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="521" spans="2:27" hidden="1">
+    <row r="521" spans="2:27">
       <c r="B521" s="54" t="s">
         <v>65</v>
       </c>
@@ -35559,7 +35558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="2:27" hidden="1">
+    <row r="522" spans="2:27">
       <c r="B522" s="54" t="s">
         <v>65</v>
       </c>
@@ -35615,7 +35614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="523" spans="2:27" hidden="1">
+    <row r="523" spans="2:27">
       <c r="B523" s="54" t="s">
         <v>65</v>
       </c>
@@ -35671,7 +35670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="2:27" hidden="1">
+    <row r="524" spans="2:27">
       <c r="B524" s="54" t="s">
         <v>65</v>
       </c>
@@ -35727,7 +35726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="525" spans="2:27" hidden="1">
+    <row r="525" spans="2:27">
       <c r="B525" s="54" t="s">
         <v>65</v>
       </c>
@@ -35783,7 +35782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="2:27" hidden="1">
+    <row r="526" spans="2:27">
       <c r="B526" s="54" t="s">
         <v>65</v>
       </c>
@@ -35839,7 +35838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="527" spans="2:27" hidden="1">
+    <row r="527" spans="2:27">
       <c r="B527" s="54" t="s">
         <v>65</v>
       </c>
@@ -35895,7 +35894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="2:27" hidden="1">
+    <row r="528" spans="2:27">
       <c r="B528" s="54" t="s">
         <v>65</v>
       </c>
@@ -35954,7 +35953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="2:30" hidden="1">
+    <row r="529" spans="2:30">
       <c r="B529" s="54" t="s">
         <v>65</v>
       </c>
@@ -36010,7 +36009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="2:30" hidden="1">
+    <row r="530" spans="2:30">
       <c r="B530" s="54" t="s">
         <v>65</v>
       </c>
@@ -36069,7 +36068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="2:30" hidden="1">
+    <row r="531" spans="2:30">
       <c r="B531" s="54" t="s">
         <v>65</v>
       </c>
@@ -36128,7 +36127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="2:30" hidden="1">
+    <row r="532" spans="2:30">
       <c r="B532" s="54" t="s">
         <v>65</v>
       </c>
@@ -36184,7 +36183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="2:30" hidden="1">
+    <row r="533" spans="2:30">
       <c r="B533" s="54" t="s">
         <v>65</v>
       </c>
@@ -36240,7 +36239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="2:30" hidden="1">
+    <row r="534" spans="2:30">
       <c r="B534" s="54" t="s">
         <v>65</v>
       </c>
@@ -36296,7 +36295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="2:30" hidden="1">
+    <row r="535" spans="2:30">
       <c r="B535" s="54" t="s">
         <v>65</v>
       </c>
@@ -36352,7 +36351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="2:30" hidden="1">
+    <row r="536" spans="2:30">
       <c r="B536" s="54" t="s">
         <v>65</v>
       </c>
@@ -36411,7 +36410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="2:30" hidden="1">
+    <row r="537" spans="2:30">
       <c r="B537" s="54" t="s">
         <v>64</v>
       </c>
@@ -36479,7 +36478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="2:30" hidden="1">
+    <row r="538" spans="2:30">
       <c r="B538" s="54" t="s">
         <v>136</v>
       </c>
@@ -36538,7 +36537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="2:30" hidden="1">
+    <row r="539" spans="2:30">
       <c r="B539" s="54" t="s">
         <v>136</v>
       </c>
@@ -36600,7 +36599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="2:30" hidden="1">
+    <row r="540" spans="2:30">
       <c r="B540" s="54" t="s">
         <v>136</v>
       </c>
@@ -36730,7 +36729,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="542" spans="2:30" hidden="1">
+    <row r="542" spans="2:30">
       <c r="B542" s="54" t="s">
         <v>64</v>
       </c>
@@ -36786,7 +36785,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="543" spans="2:30" hidden="1">
+    <row r="543" spans="2:30">
       <c r="B543" s="54" t="s">
         <v>64</v>
       </c>
@@ -36842,7 +36841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="544" spans="2:30" hidden="1">
+    <row r="544" spans="2:30">
       <c r="B544" s="54" t="s">
         <v>64</v>
       </c>
@@ -36898,7 +36897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="545" spans="2:26" hidden="1">
+    <row r="545" spans="2:26">
       <c r="B545" s="54" t="s">
         <v>64</v>
       </c>
@@ -36957,7 +36956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="2:26" hidden="1">
+    <row r="546" spans="2:26">
       <c r="B546" s="54" t="s">
         <v>64</v>
       </c>
@@ -37013,7 +37012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="547" spans="2:26" hidden="1">
+    <row r="547" spans="2:26">
       <c r="B547" s="54" t="s">
         <v>64</v>
       </c>
@@ -37081,7 +37080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="2:26" hidden="1">
+    <row r="548" spans="2:26">
       <c r="B548" s="54" t="s">
         <v>64</v>
       </c>
@@ -37193,7 +37192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="550" spans="2:26" hidden="1">
+    <row r="550" spans="2:26">
       <c r="B550" s="54" t="s">
         <v>64</v>
       </c>
@@ -37255,7 +37254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="2:26" hidden="1">
+    <row r="551" spans="2:26">
       <c r="B551" s="54" t="s">
         <v>64</v>
       </c>
@@ -37323,7 +37322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="552" spans="2:26" hidden="1">
+    <row r="552" spans="2:26">
       <c r="B552" s="54" t="s">
         <v>64</v>
       </c>
@@ -37379,7 +37378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="553" spans="2:26" hidden="1">
+    <row r="553" spans="2:26">
       <c r="B553" s="54" t="s">
         <v>64</v>
       </c>
@@ -37435,7 +37434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="554" spans="2:26" hidden="1">
+    <row r="554" spans="2:26">
       <c r="B554" s="54" t="s">
         <v>64</v>
       </c>
@@ -37491,7 +37490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="2:26" hidden="1">
+    <row r="555" spans="2:26">
       <c r="B555" s="54" t="s">
         <v>64</v>
       </c>
@@ -37547,7 +37546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="2:26" hidden="1">
+    <row r="556" spans="2:26">
       <c r="B556" s="54" t="s">
         <v>64</v>
       </c>
@@ -37659,7 +37658,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="558" spans="2:26" hidden="1">
+    <row r="558" spans="2:26">
       <c r="B558" s="54" t="s">
         <v>64</v>
       </c>
@@ -37715,7 +37714,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="559" spans="2:26" hidden="1">
+    <row r="559" spans="2:26">
       <c r="B559" s="54" t="s">
         <v>64</v>
       </c>
@@ -37780,7 +37779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="2:26" hidden="1">
+    <row r="560" spans="2:26">
       <c r="B560" s="54" t="s">
         <v>64</v>
       </c>
@@ -37836,7 +37835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="561" spans="2:26" hidden="1">
+    <row r="561" spans="2:26">
       <c r="B561" s="54" t="s">
         <v>64</v>
       </c>
@@ -37892,7 +37891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="2:26" hidden="1">
+    <row r="562" spans="2:26">
       <c r="B562" s="54" t="s">
         <v>64</v>
       </c>
@@ -37948,7 +37947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="563" spans="2:26" hidden="1">
+    <row r="563" spans="2:26">
       <c r="B563" s="54" t="s">
         <v>64</v>
       </c>
@@ -38004,7 +38003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="2:26" hidden="1">
+    <row r="564" spans="2:26">
       <c r="B564" s="54" t="s">
         <v>64</v>
       </c>
@@ -38060,7 +38059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="565" spans="2:26" hidden="1">
+    <row r="565" spans="2:26">
       <c r="B565" s="54" t="s">
         <v>64</v>
       </c>
@@ -38116,7 +38115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="566" spans="2:26" hidden="1">
+    <row r="566" spans="2:26">
       <c r="B566" s="54" t="s">
         <v>64</v>
       </c>
@@ -38178,7 +38177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="2:26" hidden="1">
+    <row r="567" spans="2:26">
       <c r="B567" s="54" t="s">
         <v>64</v>
       </c>
@@ -38234,7 +38233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="568" spans="2:26" hidden="1">
+    <row r="568" spans="2:26">
       <c r="B568" s="54" t="s">
         <v>64</v>
       </c>
@@ -38296,7 +38295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="2:26" hidden="1">
+    <row r="569" spans="2:26">
       <c r="B569" s="54" t="s">
         <v>64</v>
       </c>
@@ -38352,7 +38351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="2:26" hidden="1">
+    <row r="570" spans="2:26">
       <c r="B570" s="54" t="s">
         <v>64</v>
       </c>
@@ -38408,7 +38407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="2:26" hidden="1">
+    <row r="571" spans="2:26">
       <c r="B571" s="54" t="s">
         <v>64</v>
       </c>
@@ -38464,7 +38463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="2:26" hidden="1">
+    <row r="572" spans="2:26">
       <c r="B572" s="54" t="s">
         <v>64</v>
       </c>
@@ -38520,7 +38519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="573" spans="2:26" hidden="1">
+    <row r="573" spans="2:26">
       <c r="B573" s="54" t="s">
         <v>64</v>
       </c>
@@ -38576,7 +38575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="2:26" hidden="1">
+    <row r="574" spans="2:26">
       <c r="B574" s="54" t="s">
         <v>64</v>
       </c>
@@ -38632,7 +38631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="575" spans="2:26" hidden="1">
+    <row r="575" spans="2:26">
       <c r="B575" s="54" t="s">
         <v>64</v>
       </c>
@@ -38697,7 +38696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="2:26" hidden="1">
+    <row r="576" spans="2:26">
       <c r="B576" s="54" t="s">
         <v>64</v>
       </c>
@@ -38753,7 +38752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="2:30" hidden="1">
+    <row r="577" spans="2:30">
       <c r="B577" s="54" t="s">
         <v>64</v>
       </c>
@@ -38809,7 +38808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="2:30" hidden="1">
+    <row r="578" spans="2:30">
       <c r="B578" s="54" t="s">
         <v>64</v>
       </c>
@@ -38865,7 +38864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="2:30" hidden="1">
+    <row r="579" spans="2:30">
       <c r="B579" s="54" t="s">
         <v>64</v>
       </c>
@@ -38924,7 +38923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="2:30" hidden="1">
+    <row r="580" spans="2:30">
       <c r="B580" s="54" t="s">
         <v>64</v>
       </c>
@@ -38995,7 +38994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="581" spans="2:30" hidden="1">
+    <row r="581" spans="2:30">
       <c r="B581" s="54" t="s">
         <v>64</v>
       </c>
@@ -39063,7 +39062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="2:30" hidden="1">
+    <row r="582" spans="2:30">
       <c r="B582" s="54" t="s">
         <v>64</v>
       </c>
@@ -39187,7 +39186,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="584" spans="2:30" hidden="1">
+    <row r="584" spans="2:30">
       <c r="B584" s="54" t="s">
         <v>64</v>
       </c>
@@ -39243,7 +39242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="585" spans="2:30" hidden="1">
+    <row r="585" spans="2:30">
       <c r="B585" s="54" t="s">
         <v>64</v>
       </c>
@@ -39299,7 +39298,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="586" spans="2:30" hidden="1">
+    <row r="586" spans="2:30">
       <c r="B586" s="54" t="s">
         <v>64</v>
       </c>
@@ -39370,7 +39369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="2:30" hidden="1">
+    <row r="587" spans="2:30">
       <c r="B587" s="54" t="s">
         <v>64</v>
       </c>
@@ -39426,7 +39425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="2:30" hidden="1">
+    <row r="588" spans="2:30">
       <c r="B588" s="54" t="s">
         <v>64</v>
       </c>
@@ -39556,7 +39555,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="590" spans="2:30" hidden="1">
+    <row r="590" spans="2:30">
       <c r="B590" s="54" t="s">
         <v>64</v>
       </c>
@@ -39612,7 +39611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="2:30" hidden="1">
+    <row r="591" spans="2:30">
       <c r="B591" s="54" t="s">
         <v>64</v>
       </c>
@@ -39668,7 +39667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="2:30" hidden="1">
+    <row r="592" spans="2:30">
       <c r="B592" s="54" t="s">
         <v>64</v>
       </c>
@@ -39724,7 +39723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="593" spans="2:26" hidden="1">
+    <row r="593" spans="2:26">
       <c r="B593" s="54" t="s">
         <v>64</v>
       </c>
@@ -39786,7 +39785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="2:26" hidden="1">
+    <row r="594" spans="2:26">
       <c r="B594" s="54" t="s">
         <v>64</v>
       </c>
@@ -39842,7 +39841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="2:26" hidden="1">
+    <row r="595" spans="2:26">
       <c r="B595" s="54" t="s">
         <v>64</v>
       </c>
@@ -39898,7 +39897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="596" spans="2:26" hidden="1">
+    <row r="596" spans="2:26">
       <c r="B596" s="54" t="s">
         <v>64</v>
       </c>
@@ -39960,7 +39959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="2:26" hidden="1">
+    <row r="597" spans="2:26">
       <c r="B597" s="54" t="s">
         <v>64</v>
       </c>
@@ -40016,7 +40015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="2:26" hidden="1">
+    <row r="598" spans="2:26">
       <c r="B598" s="54" t="s">
         <v>64</v>
       </c>
@@ -40072,7 +40071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="2:26" hidden="1">
+    <row r="599" spans="2:26">
       <c r="B599" s="54" t="s">
         <v>64</v>
       </c>
@@ -40131,7 +40130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="2:26" hidden="1">
+    <row r="600" spans="2:26">
       <c r="B600" s="54" t="s">
         <v>64</v>
       </c>
@@ -40302,7 +40301,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="603" spans="2:26" hidden="1">
+    <row r="603" spans="2:26">
       <c r="B603" s="54" t="s">
         <v>64</v>
       </c>
@@ -40358,7 +40357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="604" spans="2:26" hidden="1">
+    <row r="604" spans="2:26">
       <c r="B604" s="54" t="s">
         <v>64</v>
       </c>
@@ -40414,7 +40413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="605" spans="2:26" hidden="1">
+    <row r="605" spans="2:26">
       <c r="B605" s="54" t="s">
         <v>64</v>
       </c>
@@ -40473,7 +40472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="2:26" hidden="1">
+    <row r="606" spans="2:26">
       <c r="B606" s="54" t="s">
         <v>64</v>
       </c>
@@ -40529,7 +40528,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="607" spans="2:26" hidden="1">
+    <row r="607" spans="2:26">
       <c r="B607" s="54" t="s">
         <v>64</v>
       </c>
@@ -40603,7 +40602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="2:26" hidden="1">
+    <row r="608" spans="2:26">
       <c r="B608" s="54" t="s">
         <v>64</v>
       </c>
@@ -40659,7 +40658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="2:27" hidden="1">
+    <row r="609" spans="2:27">
       <c r="B609" s="54" t="s">
         <v>64</v>
       </c>
@@ -40715,7 +40714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="2:27" hidden="1">
+    <row r="610" spans="2:27">
       <c r="B610" s="54" t="s">
         <v>64</v>
       </c>
@@ -40771,7 +40770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="2:27" hidden="1">
+    <row r="611" spans="2:27">
       <c r="B611" s="54" t="s">
         <v>64</v>
       </c>
@@ -40827,7 +40826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="612" spans="2:27" hidden="1">
+    <row r="612" spans="2:27">
       <c r="B612" s="54" t="s">
         <v>64</v>
       </c>
@@ -40883,7 +40882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="613" spans="2:27" hidden="1">
+    <row r="613" spans="2:27">
       <c r="B613" s="54" t="s">
         <v>64</v>
       </c>
@@ -40939,7 +40938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="2:27" hidden="1">
+    <row r="614" spans="2:27">
       <c r="B614" s="54" t="s">
         <v>64</v>
       </c>
@@ -40995,7 +40994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="615" spans="2:27" hidden="1">
+    <row r="615" spans="2:27">
       <c r="B615" s="54" t="s">
         <v>64</v>
       </c>
@@ -41057,7 +41056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="2:27" hidden="1">
+    <row r="616" spans="2:27">
       <c r="B616" s="54" t="s">
         <v>64</v>
       </c>
@@ -41113,7 +41112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="2:27" hidden="1">
+    <row r="617" spans="2:27">
       <c r="B617" s="54" t="s">
         <v>64</v>
       </c>
@@ -41172,7 +41171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="2:27" hidden="1">
+    <row r="618" spans="2:27">
       <c r="B618" s="54" t="s">
         <v>64</v>
       </c>
@@ -41228,7 +41227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="2:27" hidden="1">
+    <row r="619" spans="2:27">
       <c r="B619" s="54" t="s">
         <v>64</v>
       </c>
@@ -41284,7 +41283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="2:27" hidden="1">
+    <row r="620" spans="2:27">
       <c r="B620" s="54" t="s">
         <v>64</v>
       </c>
@@ -41340,7 +41339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="621" spans="2:27" hidden="1">
+    <row r="621" spans="2:27">
       <c r="B621" s="54" t="s">
         <v>64</v>
       </c>
@@ -41396,7 +41395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="2:27" hidden="1">
+    <row r="622" spans="2:27">
       <c r="B622" s="54" t="s">
         <v>64</v>
       </c>
@@ -41452,7 +41451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="2:27" hidden="1">
+    <row r="623" spans="2:27">
       <c r="B623" s="54" t="s">
         <v>64</v>
       </c>
@@ -41511,7 +41510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="2:27" hidden="1">
+    <row r="624" spans="2:27">
       <c r="B624" s="54" t="s">
         <v>64</v>
       </c>
@@ -41570,7 +41569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="2:30" hidden="1">
+    <row r="625" spans="2:30">
       <c r="B625" s="54" t="s">
         <v>64</v>
       </c>
@@ -41629,7 +41628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="2:30" hidden="1">
+    <row r="626" spans="2:30">
       <c r="B626" s="54" t="s">
         <v>64</v>
       </c>
@@ -41688,7 +41687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="2:30" hidden="1">
+    <row r="627" spans="2:30">
       <c r="B627" s="54" t="s">
         <v>64</v>
       </c>
@@ -41744,7 +41743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="2:30" hidden="1">
+    <row r="628" spans="2:30">
       <c r="B628" s="54" t="s">
         <v>64</v>
       </c>
@@ -41800,7 +41799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="2:30" hidden="1">
+    <row r="629" spans="2:30">
       <c r="B629" s="54" t="s">
         <v>64</v>
       </c>
@@ -41856,7 +41855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="2:30" hidden="1">
+    <row r="630" spans="2:30">
       <c r="B630" s="54" t="s">
         <v>64</v>
       </c>
@@ -41912,7 +41911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="2:30" hidden="1">
+    <row r="631" spans="2:30">
       <c r="B631" s="54" t="s">
         <v>64</v>
       </c>
@@ -41968,7 +41967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="2:30" hidden="1">
+    <row r="632" spans="2:30">
       <c r="B632" s="54" t="s">
         <v>136</v>
       </c>
@@ -42027,7 +42026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="2:30" hidden="1">
+    <row r="633" spans="2:30">
       <c r="B633" s="54" t="s">
         <v>136</v>
       </c>
@@ -42092,7 +42091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="2:30" hidden="1">
+    <row r="634" spans="2:30">
       <c r="B634" s="54" t="s">
         <v>136</v>
       </c>
@@ -42154,7 +42153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="2:30" hidden="1">
+    <row r="635" spans="2:30">
       <c r="B635" s="54" t="s">
         <v>136</v>
       </c>
@@ -42216,7 +42215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="2:30" hidden="1">
+    <row r="636" spans="2:30">
       <c r="B636" s="54" t="s">
         <v>136</v>
       </c>
@@ -42275,7 +42274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="637" spans="2:30" hidden="1">
+    <row r="637" spans="2:30">
       <c r="B637" s="54" t="s">
         <v>136</v>
       </c>
@@ -42334,7 +42333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="2:30" hidden="1">
+    <row r="638" spans="2:30">
       <c r="B638" s="54" t="s">
         <v>136</v>
       </c>
@@ -42446,7 +42445,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="640" spans="2:30" hidden="1">
+    <row r="640" spans="2:30">
       <c r="B640" s="54" t="s">
         <v>136</v>
       </c>
@@ -42558,7 +42557,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="642" spans="2:25" hidden="1">
+    <row r="642" spans="2:25">
       <c r="B642" s="54" t="s">
         <v>136</v>
       </c>
@@ -42626,7 +42625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="2:25" hidden="1">
+    <row r="643" spans="2:25">
       <c r="B643" s="54" t="s">
         <v>136</v>
       </c>
@@ -42682,7 +42681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="644" spans="2:25" hidden="1">
+    <row r="644" spans="2:25">
       <c r="B644" s="54" t="s">
         <v>136</v>
       </c>
@@ -42738,7 +42737,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="645" spans="2:25" hidden="1">
+    <row r="645" spans="2:25">
       <c r="B645" s="54" t="s">
         <v>136</v>
       </c>
@@ -42794,7 +42793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="646" spans="2:25" hidden="1">
+    <row r="646" spans="2:25">
       <c r="B646" s="54" t="s">
         <v>136</v>
       </c>
@@ -42850,7 +42849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="2:25" hidden="1">
+    <row r="647" spans="2:25">
       <c r="B647" s="54" t="s">
         <v>136</v>
       </c>
@@ -42906,7 +42905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="2:25" hidden="1">
+    <row r="648" spans="2:25">
       <c r="B648" s="54" t="s">
         <v>136</v>
       </c>
@@ -42968,7 +42967,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="649" spans="2:25" hidden="1">
+    <row r="649" spans="2:25">
       <c r="B649" s="54" t="s">
         <v>136</v>
       </c>
@@ -43024,7 +43023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="2:25" hidden="1">
+    <row r="650" spans="2:25">
       <c r="B650" s="54" t="s">
         <v>136</v>
       </c>
@@ -43080,7 +43079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="651" spans="2:25" hidden="1">
+    <row r="651" spans="2:25">
       <c r="B651" s="54" t="s">
         <v>136</v>
       </c>
@@ -43136,7 +43135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="2:25" hidden="1">
+    <row r="652" spans="2:25">
       <c r="B652" s="54" t="s">
         <v>136</v>
       </c>
@@ -43192,7 +43191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="653" spans="2:25" hidden="1">
+    <row r="653" spans="2:25">
       <c r="B653" s="54" t="s">
         <v>136</v>
       </c>
@@ -43260,7 +43259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="2:25" hidden="1">
+    <row r="654" spans="2:25">
       <c r="B654" s="54" t="s">
         <v>136</v>
       </c>
@@ -43316,7 +43315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="655" spans="2:25" hidden="1">
+    <row r="655" spans="2:25">
       <c r="B655" s="54" t="s">
         <v>136</v>
       </c>
@@ -43428,7 +43427,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="657" spans="2:32" hidden="1">
+    <row r="657" spans="2:32">
       <c r="B657" s="54" t="s">
         <v>136</v>
       </c>
@@ -43540,7 +43539,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="659" spans="2:32" hidden="1">
+    <row r="659" spans="2:32">
       <c r="B659" s="54" t="s">
         <v>136</v>
       </c>
@@ -43596,7 +43595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="660" spans="2:32" hidden="1">
+    <row r="660" spans="2:32">
       <c r="B660" s="54" t="s">
         <v>136</v>
       </c>
@@ -43652,7 +43651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="2:32" hidden="1">
+    <row r="661" spans="2:32">
       <c r="B661" s="54" t="s">
         <v>136</v>
       </c>
@@ -43711,7 +43710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="662" spans="2:32" hidden="1">
+    <row r="662" spans="2:32">
       <c r="B662" s="54" t="s">
         <v>136</v>
       </c>
@@ -43767,7 +43766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="2:32" hidden="1">
+    <row r="663" spans="2:32">
       <c r="B663" s="54" t="s">
         <v>136</v>
       </c>
@@ -43823,7 +43822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="664" spans="2:32" hidden="1">
+    <row r="664" spans="2:32">
       <c r="B664" s="54" t="s">
         <v>136</v>
       </c>
@@ -43882,7 +43881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="665" spans="2:32" hidden="1">
+    <row r="665" spans="2:32">
       <c r="B665" s="54" t="s">
         <v>136</v>
       </c>
@@ -43947,7 +43946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="2:32" hidden="1">
+    <row r="666" spans="2:32">
       <c r="B666" s="54" t="s">
         <v>136</v>
       </c>
@@ -44003,7 +44002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="667" spans="2:32" hidden="1">
+    <row r="667" spans="2:32">
       <c r="B667" s="54" t="s">
         <v>136</v>
       </c>
@@ -44059,7 +44058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="2:32" hidden="1">
+    <row r="668" spans="2:32">
       <c r="B668" s="54" t="s">
         <v>136</v>
       </c>
@@ -44115,7 +44114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="669" spans="2:32" hidden="1">
+    <row r="669" spans="2:32">
       <c r="B669" s="54" t="s">
         <v>136</v>
       </c>
@@ -44174,7 +44173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="670" spans="2:32" hidden="1">
+    <row r="670" spans="2:32">
       <c r="B670" s="54" t="s">
         <v>136</v>
       </c>
@@ -44233,7 +44232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="2:32" hidden="1">
+    <row r="671" spans="2:32">
       <c r="B671" s="54" t="s">
         <v>136</v>
       </c>
@@ -44289,7 +44288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="672" spans="2:32" hidden="1">
+    <row r="672" spans="2:32">
       <c r="B672" s="54" t="s">
         <v>136</v>
       </c>
@@ -44345,7 +44344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="673" spans="2:30" hidden="1">
+    <row r="673" spans="2:30">
       <c r="B673" s="54" t="s">
         <v>136</v>
       </c>
@@ -44407,7 +44406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="2:30" hidden="1">
+    <row r="674" spans="2:30">
       <c r="B674" s="54" t="s">
         <v>136</v>
       </c>
@@ -44466,7 +44465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="675" spans="2:30" hidden="1">
+    <row r="675" spans="2:30">
       <c r="B675" s="54" t="s">
         <v>136</v>
       </c>
@@ -44522,7 +44521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="2:30" hidden="1">
+    <row r="676" spans="2:30">
       <c r="B676" s="54" t="s">
         <v>136</v>
       </c>
@@ -44578,7 +44577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="2:30" hidden="1">
+    <row r="677" spans="2:30">
       <c r="B677" s="54" t="s">
         <v>136</v>
       </c>
@@ -44634,7 +44633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="2:30" hidden="1">
+    <row r="678" spans="2:30">
       <c r="B678" s="54" t="s">
         <v>136</v>
       </c>
@@ -44690,7 +44689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="2:30" hidden="1">
+    <row r="679" spans="2:30">
       <c r="B679" s="54" t="s">
         <v>64</v>
       </c>
@@ -44758,7 +44757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="2:30" hidden="1">
+    <row r="680" spans="2:30">
       <c r="B680" s="54" t="s">
         <v>64</v>
       </c>
@@ -44817,7 +44816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="2:30" hidden="1">
+    <row r="681" spans="2:30">
       <c r="B681" s="54" t="s">
         <v>64</v>
       </c>
@@ -44876,7 +44875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="682" spans="2:30" hidden="1">
+    <row r="682" spans="2:30">
       <c r="B682" s="54" t="s">
         <v>64</v>
       </c>
@@ -44938,7 +44937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="2:30" hidden="1">
+    <row r="683" spans="2:30">
       <c r="B683" s="54" t="s">
         <v>64</v>
       </c>
@@ -44997,7 +44996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="684" spans="2:30" hidden="1">
+    <row r="684" spans="2:30">
       <c r="B684" s="54" t="s">
         <v>64</v>
       </c>
@@ -45056,7 +45055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="685" spans="2:30" hidden="1">
+    <row r="685" spans="2:30">
       <c r="B685" s="54" t="s">
         <v>64</v>
       </c>
@@ -45168,7 +45167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="687" spans="2:30" hidden="1">
+    <row r="687" spans="2:30">
       <c r="B687" s="54" t="s">
         <v>64</v>
       </c>
@@ -45239,7 +45238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="2:30" hidden="1">
+    <row r="688" spans="2:30">
       <c r="B688" s="54" t="s">
         <v>64</v>
       </c>
@@ -45295,7 +45294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="689" spans="2:26" hidden="1">
+    <row r="689" spans="2:26">
       <c r="B689" s="54" t="s">
         <v>64</v>
       </c>
@@ -45351,7 +45350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690" spans="2:26" hidden="1">
+    <row r="690" spans="2:26">
       <c r="B690" s="54" t="s">
         <v>64</v>
       </c>
@@ -45407,7 +45406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="691" spans="2:26" hidden="1">
+    <row r="691" spans="2:26">
       <c r="B691" s="54" t="s">
         <v>64</v>
       </c>
@@ -45463,7 +45462,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="692" spans="2:26" hidden="1">
+    <row r="692" spans="2:26">
       <c r="B692" s="54" t="s">
         <v>64</v>
       </c>
@@ -45519,7 +45518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="693" spans="2:26" hidden="1">
+    <row r="693" spans="2:26">
       <c r="B693" s="54" t="s">
         <v>64</v>
       </c>
@@ -45575,7 +45574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="694" spans="2:26" hidden="1">
+    <row r="694" spans="2:26">
       <c r="B694" s="54" t="s">
         <v>64</v>
       </c>
@@ -45643,7 +45642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="2:26" hidden="1">
+    <row r="695" spans="2:26">
       <c r="B695" s="54" t="s">
         <v>64</v>
       </c>
@@ -45699,7 +45698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="696" spans="2:26" hidden="1">
+    <row r="696" spans="2:26">
       <c r="B696" s="54" t="s">
         <v>64</v>
       </c>
@@ -45755,7 +45754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="2:26" hidden="1">
+    <row r="697" spans="2:26">
       <c r="B697" s="54" t="s">
         <v>64</v>
       </c>
@@ -45867,7 +45866,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="699" spans="2:26" hidden="1">
+    <row r="699" spans="2:26">
       <c r="B699" s="54" t="s">
         <v>64</v>
       </c>
@@ -45923,7 +45922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="700" spans="2:26" hidden="1">
+    <row r="700" spans="2:26">
       <c r="B700" s="54" t="s">
         <v>64</v>
       </c>
@@ -45979,7 +45978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="701" spans="2:26" hidden="1">
+    <row r="701" spans="2:26">
       <c r="B701" s="54" t="s">
         <v>64</v>
       </c>
@@ -46035,7 +46034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="702" spans="2:26" hidden="1">
+    <row r="702" spans="2:26">
       <c r="B702" s="54" t="s">
         <v>64</v>
       </c>
@@ -46103,7 +46102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="703" spans="2:26" hidden="1">
+    <row r="703" spans="2:26">
       <c r="B703" s="54" t="s">
         <v>64</v>
       </c>
@@ -46159,7 +46158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="704" spans="2:26" hidden="1">
+    <row r="704" spans="2:26">
       <c r="B704" s="54" t="s">
         <v>64</v>
       </c>
@@ -46215,7 +46214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="705" spans="2:28" hidden="1">
+    <row r="705" spans="2:28">
       <c r="B705" s="54" t="s">
         <v>64</v>
       </c>
@@ -46271,7 +46270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="706" spans="2:28" hidden="1">
+    <row r="706" spans="2:28">
       <c r="B706" s="54" t="s">
         <v>64</v>
       </c>
@@ -46327,7 +46326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="707" spans="2:28" hidden="1">
+    <row r="707" spans="2:28">
       <c r="B707" s="54" t="s">
         <v>64</v>
       </c>
@@ -46383,7 +46382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="708" spans="2:28" hidden="1">
+    <row r="708" spans="2:28">
       <c r="B708" s="54" t="s">
         <v>64</v>
       </c>
@@ -46439,7 +46438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="2:28" hidden="1">
+    <row r="709" spans="2:28">
       <c r="B709" s="54" t="s">
         <v>64</v>
       </c>
@@ -46495,7 +46494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="710" spans="2:28" hidden="1">
+    <row r="710" spans="2:28">
       <c r="B710" s="54" t="s">
         <v>64</v>
       </c>
@@ -46554,7 +46553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" spans="2:28" hidden="1">
+    <row r="711" spans="2:28">
       <c r="B711" s="54" t="s">
         <v>64</v>
       </c>
@@ -46610,7 +46609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" spans="2:28" hidden="1">
+    <row r="712" spans="2:28">
       <c r="B712" s="54" t="s">
         <v>64</v>
       </c>
@@ -46666,7 +46665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="713" spans="2:28" hidden="1">
+    <row r="713" spans="2:28">
       <c r="B713" s="54" t="s">
         <v>64</v>
       </c>
@@ -46722,7 +46721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="2:28" hidden="1">
+    <row r="714" spans="2:28">
       <c r="B714" s="54" t="s">
         <v>64</v>
       </c>
@@ -46778,7 +46777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="715" spans="2:28" hidden="1">
+    <row r="715" spans="2:28">
       <c r="B715" s="54" t="s">
         <v>64</v>
       </c>
@@ -46834,7 +46833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="716" spans="2:28" hidden="1">
+    <row r="716" spans="2:28">
       <c r="B716" s="54" t="s">
         <v>64</v>
       </c>
@@ -46893,7 +46892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="717" spans="2:28" hidden="1">
+    <row r="717" spans="2:28">
       <c r="B717" s="54" t="s">
         <v>64</v>
       </c>
@@ -46952,7 +46951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="718" spans="2:28" hidden="1">
+    <row r="718" spans="2:28">
       <c r="B718" s="54" t="s">
         <v>64</v>
       </c>
@@ -47008,7 +47007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="719" spans="2:28" hidden="1">
+    <row r="719" spans="2:28">
       <c r="B719" s="54" t="s">
         <v>64</v>
       </c>
@@ -47064,7 +47063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="720" spans="2:28" hidden="1">
+    <row r="720" spans="2:28">
       <c r="B720" s="54" t="s">
         <v>64</v>
       </c>
@@ -47120,7 +47119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="721" spans="2:30" hidden="1">
+    <row r="721" spans="2:30">
       <c r="B721" s="54" t="s">
         <v>64</v>
       </c>
@@ -47176,7 +47175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="722" spans="2:30" hidden="1">
+    <row r="722" spans="2:30">
       <c r="B722" s="54" t="s">
         <v>64</v>
       </c>
@@ -47232,7 +47231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="723" spans="2:30" hidden="1">
+    <row r="723" spans="2:30">
       <c r="B723" s="54" t="s">
         <v>64</v>
       </c>
@@ -47288,7 +47287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="724" spans="2:30" hidden="1">
+    <row r="724" spans="2:30">
       <c r="B724" s="54" t="s">
         <v>64</v>
       </c>
@@ -47359,7 +47358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="2:30" hidden="1">
+    <row r="725" spans="2:30">
       <c r="B725" s="54" t="s">
         <v>64</v>
       </c>
@@ -47418,7 +47417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="726" spans="2:30" hidden="1">
+    <row r="726" spans="2:30">
       <c r="B726" s="54" t="s">
         <v>64</v>
       </c>
@@ -47477,7 +47476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="2:30" hidden="1">
+    <row r="727" spans="2:30">
       <c r="B727" s="54" t="s">
         <v>64</v>
       </c>
@@ -47536,7 +47535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="728" spans="2:30" hidden="1">
+    <row r="728" spans="2:30">
       <c r="B728" s="54" t="s">
         <v>65</v>
       </c>
@@ -47595,7 +47594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="2:30" hidden="1">
+    <row r="729" spans="2:30">
       <c r="B729" s="54" t="s">
         <v>65</v>
       </c>
@@ -47722,7 +47721,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="731" spans="2:30" hidden="1">
+    <row r="731" spans="2:30">
       <c r="B731" s="54" t="s">
         <v>64</v>
       </c>
@@ -47834,7 +47833,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="733" spans="2:30" hidden="1">
+    <row r="733" spans="2:30">
       <c r="B733" s="54" t="s">
         <v>64</v>
       </c>
@@ -47890,7 +47889,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="734" spans="2:30" hidden="1">
+    <row r="734" spans="2:30">
       <c r="B734" s="54" t="s">
         <v>64</v>
       </c>
@@ -47961,7 +47960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="735" spans="2:30" hidden="1">
+    <row r="735" spans="2:30">
       <c r="B735" s="54" t="s">
         <v>64</v>
       </c>
@@ -48023,7 +48022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="736" spans="2:30" hidden="1">
+    <row r="736" spans="2:30">
       <c r="B736" s="54" t="s">
         <v>64</v>
       </c>
@@ -48088,7 +48087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="737" spans="2:25" hidden="1">
+    <row r="737" spans="2:25">
       <c r="B737" s="54" t="s">
         <v>64</v>
       </c>
@@ -48144,7 +48143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="738" spans="2:25" hidden="1">
+    <row r="738" spans="2:25">
       <c r="B738" s="54" t="s">
         <v>64</v>
       </c>
@@ -48200,7 +48199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="739" spans="2:25" hidden="1">
+    <row r="739" spans="2:25">
       <c r="B739" s="54" t="s">
         <v>64</v>
       </c>
@@ -48256,7 +48255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="740" spans="2:25" hidden="1">
+    <row r="740" spans="2:25">
       <c r="B740" s="54" t="s">
         <v>64</v>
       </c>
@@ -48312,7 +48311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="741" spans="2:25" hidden="1">
+    <row r="741" spans="2:25">
       <c r="B741" s="54" t="s">
         <v>64</v>
       </c>
@@ -48368,7 +48367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="742" spans="2:25" hidden="1">
+    <row r="742" spans="2:25">
       <c r="B742" s="54" t="s">
         <v>64</v>
       </c>
@@ -48427,7 +48426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="743" spans="2:25" hidden="1">
+    <row r="743" spans="2:25">
       <c r="B743" s="54" t="s">
         <v>64</v>
       </c>
@@ -48483,7 +48482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="744" spans="2:25" hidden="1">
+    <row r="744" spans="2:25">
       <c r="B744" s="54" t="s">
         <v>64</v>
       </c>
@@ -48539,7 +48538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="745" spans="2:25" hidden="1">
+    <row r="745" spans="2:25">
       <c r="B745" s="54" t="s">
         <v>64</v>
       </c>
@@ -48595,7 +48594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="2:25" hidden="1">
+    <row r="746" spans="2:25">
       <c r="B746" s="54" t="s">
         <v>64</v>
       </c>
@@ -48651,7 +48650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="747" spans="2:25" hidden="1">
+    <row r="747" spans="2:25">
       <c r="B747" s="54" t="s">
         <v>65</v>
       </c>
@@ -48707,7 +48706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="748" spans="2:25" hidden="1">
+    <row r="748" spans="2:25">
       <c r="B748" s="54" t="s">
         <v>65</v>
       </c>
@@ -48763,7 +48762,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="749" spans="2:25" hidden="1">
+    <row r="749" spans="2:25">
       <c r="B749" s="54" t="s">
         <v>65</v>
       </c>
@@ -48834,7 +48833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="750" spans="2:25" hidden="1">
+    <row r="750" spans="2:25">
       <c r="B750" s="54" t="s">
         <v>65</v>
       </c>
@@ -48890,7 +48889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="751" spans="2:25" hidden="1">
+    <row r="751" spans="2:25">
       <c r="B751" s="54" t="s">
         <v>65</v>
       </c>
@@ -49008,7 +49007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="753" spans="2:33" hidden="1">
+    <row r="753" spans="2:33">
       <c r="B753" s="54" t="s">
         <v>65</v>
       </c>
@@ -49064,7 +49063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="754" spans="2:33" hidden="1">
+    <row r="754" spans="2:33">
       <c r="B754" s="54" t="s">
         <v>65</v>
       </c>
@@ -49120,7 +49119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="2:33" hidden="1">
+    <row r="755" spans="2:33">
       <c r="B755" s="54" t="s">
         <v>65</v>
       </c>
@@ -49176,7 +49175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="2:33" hidden="1">
+    <row r="756" spans="2:33">
       <c r="B756" s="54" t="s">
         <v>65</v>
       </c>
@@ -49232,7 +49231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="757" spans="2:33" hidden="1">
+    <row r="757" spans="2:33">
       <c r="B757" s="54" t="s">
         <v>65</v>
       </c>
@@ -49288,7 +49287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="758" spans="2:33" hidden="1">
+    <row r="758" spans="2:33">
       <c r="B758" s="54" t="s">
         <v>65</v>
       </c>
@@ -49344,7 +49343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="759" spans="2:33" hidden="1">
+    <row r="759" spans="2:33">
       <c r="B759" s="54" t="s">
         <v>65</v>
       </c>
@@ -49400,7 +49399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="760" spans="2:33" hidden="1">
+    <row r="760" spans="2:33">
       <c r="B760" s="54" t="s">
         <v>65</v>
       </c>
@@ -49518,7 +49517,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="762" spans="2:33" hidden="1">
+    <row r="762" spans="2:33">
       <c r="B762" s="54" t="s">
         <v>65</v>
       </c>
@@ -49583,7 +49582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="763" spans="2:33" hidden="1">
+    <row r="763" spans="2:33">
       <c r="B763" s="54" t="s">
         <v>65</v>
       </c>
@@ -49642,7 +49641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="764" spans="2:33" hidden="1">
+    <row r="764" spans="2:33">
       <c r="B764" s="54" t="s">
         <v>65</v>
       </c>
@@ -49698,7 +49697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="765" spans="2:33" hidden="1">
+    <row r="765" spans="2:33">
       <c r="B765" s="54" t="s">
         <v>65</v>
       </c>
@@ -49754,7 +49753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="2:33" hidden="1">
+    <row r="766" spans="2:33">
       <c r="B766" s="54" t="s">
         <v>65</v>
       </c>
@@ -49810,7 +49809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="767" spans="2:33" hidden="1">
+    <row r="767" spans="2:33">
       <c r="B767" s="54" t="s">
         <v>65</v>
       </c>
@@ -49869,7 +49868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="2:33" hidden="1">
+    <row r="768" spans="2:33">
       <c r="B768" s="54" t="s">
         <v>65</v>
       </c>
@@ -49928,7 +49927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="2:33" hidden="1">
+    <row r="769" spans="2:33">
       <c r="B769" s="54" t="s">
         <v>65</v>
       </c>
@@ -49993,7 +49992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="770" spans="2:33" hidden="1">
+    <row r="770" spans="2:33">
       <c r="B770" s="54" t="s">
         <v>65</v>
       </c>
@@ -50052,7 +50051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="2:33" hidden="1">
+    <row r="771" spans="2:33">
       <c r="B771" s="54" t="s">
         <v>65</v>
       </c>
@@ -50111,7 +50110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="772" spans="2:33" hidden="1">
+    <row r="772" spans="2:33">
       <c r="B772" s="54" t="s">
         <v>65</v>
       </c>
@@ -50170,7 +50169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="773" spans="2:33" hidden="1">
+    <row r="773" spans="2:33">
       <c r="B773" s="54" t="s">
         <v>64</v>
       </c>
@@ -50229,7 +50228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="774" spans="2:33" hidden="1">
+    <row r="774" spans="2:33">
       <c r="B774" s="54" t="s">
         <v>64</v>
       </c>
@@ -50288,7 +50287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="2:33" hidden="1">
+    <row r="775" spans="2:33">
       <c r="B775" s="54" t="s">
         <v>64</v>
       </c>
@@ -50347,7 +50346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="776" spans="2:33" hidden="1">
+    <row r="776" spans="2:33">
       <c r="B776" s="54" t="s">
         <v>65</v>
       </c>
@@ -50409,7 +50408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="2:33" hidden="1">
+    <row r="777" spans="2:33">
       <c r="B777" s="54" t="s">
         <v>65</v>
       </c>
@@ -50471,7 +50470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="778" spans="2:33" hidden="1">
+    <row r="778" spans="2:33">
       <c r="B778" s="54" t="s">
         <v>65</v>
       </c>
@@ -50530,7 +50529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="779" spans="2:33" hidden="1">
+    <row r="779" spans="2:33">
       <c r="B779" s="54" t="s">
         <v>65</v>
       </c>
@@ -50586,7 +50585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="780" spans="2:33" hidden="1">
+    <row r="780" spans="2:33">
       <c r="B780" s="54" t="s">
         <v>65</v>
       </c>
@@ -50642,7 +50641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="781" spans="2:33" hidden="1">
+    <row r="781" spans="2:33">
       <c r="B781" s="54" t="s">
         <v>65</v>
       </c>
@@ -50754,7 +50753,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="783" spans="2:33" hidden="1">
+    <row r="783" spans="2:33">
       <c r="B783" s="54" t="s">
         <v>65</v>
       </c>
@@ -50810,7 +50809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="784" spans="2:33" hidden="1">
+    <row r="784" spans="2:33">
       <c r="B784" s="54" t="s">
         <v>65</v>
       </c>
@@ -50866,7 +50865,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="785" spans="2:25" hidden="1">
+    <row r="785" spans="2:25">
       <c r="B785" s="54" t="s">
         <v>65</v>
       </c>
@@ -50922,7 +50921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="786" spans="2:25" hidden="1">
+    <row r="786" spans="2:25">
       <c r="B786" s="54" t="s">
         <v>65</v>
       </c>
@@ -50978,7 +50977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="787" spans="2:25" hidden="1">
+    <row r="787" spans="2:25">
       <c r="B787" s="54" t="s">
         <v>65</v>
       </c>
@@ -51040,7 +51039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="788" spans="2:25" hidden="1">
+    <row r="788" spans="2:25">
       <c r="B788" s="54" t="s">
         <v>65</v>
       </c>
@@ -51161,7 +51160,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="790" spans="2:25" hidden="1">
+    <row r="790" spans="2:25">
       <c r="B790" s="54" t="s">
         <v>65</v>
       </c>
@@ -51217,7 +51216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="791" spans="2:25" hidden="1">
+    <row r="791" spans="2:25">
       <c r="B791" s="54" t="s">
         <v>65</v>
       </c>
@@ -51273,7 +51272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="792" spans="2:25" hidden="1">
+    <row r="792" spans="2:25">
       <c r="B792" s="54" t="s">
         <v>65</v>
       </c>
@@ -51329,7 +51328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="793" spans="2:25" hidden="1">
+    <row r="793" spans="2:25">
       <c r="B793" s="54" t="s">
         <v>65</v>
       </c>
@@ -51388,7 +51387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="2:25" hidden="1">
+    <row r="794" spans="2:25">
       <c r="B794" s="54" t="s">
         <v>65</v>
       </c>
@@ -51500,7 +51499,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="796" spans="2:25" hidden="1">
+    <row r="796" spans="2:25">
       <c r="B796" s="54" t="s">
         <v>64</v>
       </c>
@@ -51556,7 +51555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="797" spans="2:25" hidden="1">
+    <row r="797" spans="2:25">
       <c r="B797" s="54" t="s">
         <v>64</v>
       </c>
@@ -51668,7 +51667,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="799" spans="2:25" hidden="1">
+    <row r="799" spans="2:25">
       <c r="B799" s="54" t="s">
         <v>64</v>
       </c>
@@ -51724,7 +51723,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="800" spans="2:25" hidden="1">
+    <row r="800" spans="2:25">
       <c r="B800" s="54" t="s">
         <v>64</v>
       </c>
@@ -51780,7 +51779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="801" spans="2:29" hidden="1">
+    <row r="801" spans="2:29">
       <c r="B801" s="54" t="s">
         <v>64</v>
       </c>
@@ -51842,7 +51841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="802" spans="2:29" hidden="1">
+    <row r="802" spans="2:29">
       <c r="B802" s="54" t="s">
         <v>64</v>
       </c>
@@ -51898,7 +51897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="803" spans="2:29" hidden="1">
+    <row r="803" spans="2:29">
       <c r="B803" s="54" t="s">
         <v>64</v>
       </c>
@@ -51954,7 +51953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="804" spans="2:29" hidden="1">
+    <row r="804" spans="2:29">
       <c r="B804" s="54" t="s">
         <v>64</v>
       </c>
@@ -52010,7 +52009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="805" spans="2:29" hidden="1">
+    <row r="805" spans="2:29">
       <c r="B805" s="54" t="s">
         <v>64</v>
       </c>
@@ -52069,7 +52068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="806" spans="2:29" hidden="1">
+    <row r="806" spans="2:29">
       <c r="B806" s="54" t="s">
         <v>64</v>
       </c>
@@ -52134,7 +52133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="807" spans="2:29" hidden="1">
+    <row r="807" spans="2:29">
       <c r="B807" s="54" t="s">
         <v>64</v>
       </c>
@@ -52190,7 +52189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="808" spans="2:29" hidden="1">
+    <row r="808" spans="2:29">
       <c r="B808" s="54" t="s">
         <v>64</v>
       </c>
@@ -52246,7 +52245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="809" spans="2:29" hidden="1">
+    <row r="809" spans="2:29">
       <c r="B809" s="54" t="s">
         <v>64</v>
       </c>
@@ -52302,7 +52301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="810" spans="2:29" hidden="1">
+    <row r="810" spans="2:29">
       <c r="B810" s="54" t="s">
         <v>64</v>
       </c>
@@ -52358,7 +52357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="811" spans="2:29" hidden="1">
+    <row r="811" spans="2:29">
       <c r="B811" s="54" t="s">
         <v>64</v>
       </c>
@@ -52414,7 +52413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="812" spans="2:29" hidden="1">
+    <row r="812" spans="2:29">
       <c r="B812" s="54" t="s">
         <v>64</v>
       </c>
@@ -52473,7 +52472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="813" spans="2:29" hidden="1">
+    <row r="813" spans="2:29">
       <c r="B813" s="54" t="s">
         <v>64</v>
       </c>
@@ -52538,7 +52537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="814" spans="2:29" hidden="1">
+    <row r="814" spans="2:29">
       <c r="B814" s="54" t="s">
         <v>64</v>
       </c>
@@ -52597,7 +52596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="815" spans="2:29" hidden="1">
+    <row r="815" spans="2:29">
       <c r="B815" s="54" t="s">
         <v>64</v>
       </c>
@@ -52656,7 +52655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="816" spans="2:29" hidden="1">
+    <row r="816" spans="2:29">
       <c r="B816" s="54" t="s">
         <v>64</v>
       </c>
@@ -52712,7 +52711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="817" spans="2:30" hidden="1">
+    <row r="817" spans="2:30">
       <c r="B817" s="54" t="s">
         <v>65</v>
       </c>
@@ -52771,7 +52770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="818" spans="2:30" hidden="1">
+    <row r="818" spans="2:30">
       <c r="B818" s="54" t="s">
         <v>65</v>
       </c>
@@ -52830,7 +52829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="819" spans="2:30" hidden="1">
+    <row r="819" spans="2:30">
       <c r="B819" s="54" t="s">
         <v>65</v>
       </c>
@@ -52889,7 +52888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="820" spans="2:30" hidden="1">
+    <row r="820" spans="2:30">
       <c r="B820" s="54" t="s">
         <v>65</v>
       </c>
@@ -52948,7 +52947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="821" spans="2:30" hidden="1">
+    <row r="821" spans="2:30">
       <c r="B821" s="54" t="s">
         <v>65</v>
       </c>
@@ -53010,7 +53009,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="822" spans="2:30" hidden="1">
+    <row r="822" spans="2:30">
       <c r="B822" s="54" t="s">
         <v>65</v>
       </c>
@@ -53072,7 +53071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="823" spans="2:30" hidden="1">
+    <row r="823" spans="2:30">
       <c r="B823" s="54" t="s">
         <v>64</v>
       </c>
@@ -53140,7 +53139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="824" spans="2:30" hidden="1">
+    <row r="824" spans="2:30">
       <c r="B824" s="54" t="s">
         <v>64</v>
       </c>
@@ -53202,7 +53201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="825" spans="2:30" hidden="1">
+    <row r="825" spans="2:30">
       <c r="B825" s="54" t="s">
         <v>64</v>
       </c>
@@ -53267,7 +53266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="826" spans="2:30" hidden="1">
+    <row r="826" spans="2:30">
       <c r="B826" s="54" t="s">
         <v>64</v>
       </c>
@@ -53344,7 +53343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="827" spans="2:30" hidden="1">
+    <row r="827" spans="2:30">
       <c r="B827" s="54" t="s">
         <v>64</v>
       </c>
@@ -53403,7 +53402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="828" spans="2:30" hidden="1">
+    <row r="828" spans="2:30">
       <c r="B828" s="54" t="s">
         <v>64</v>
       </c>
@@ -53468,7 +53467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="829" spans="2:30" hidden="1">
+    <row r="829" spans="2:30">
       <c r="B829" s="54" t="s">
         <v>64</v>
       </c>
@@ -53530,7 +53529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="830" spans="2:30" hidden="1">
+    <row r="830" spans="2:30">
       <c r="B830" s="54" t="s">
         <v>65</v>
       </c>
@@ -53586,7 +53585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="831" spans="2:30" hidden="1">
+    <row r="831" spans="2:30">
       <c r="B831" s="54" t="s">
         <v>65</v>
       </c>
@@ -53642,7 +53641,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="832" spans="2:30" hidden="1">
+    <row r="832" spans="2:30">
       <c r="B832" s="54" t="s">
         <v>65</v>
       </c>
@@ -53713,7 +53712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="833" spans="2:28" hidden="1">
+    <row r="833" spans="2:28">
       <c r="B833" s="54" t="s">
         <v>65</v>
       </c>
@@ -53784,7 +53783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="834" spans="2:28" hidden="1">
+    <row r="834" spans="2:28">
       <c r="B834" s="54" t="s">
         <v>65</v>
       </c>
@@ -53840,7 +53839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="835" spans="2:28" hidden="1">
+    <row r="835" spans="2:28">
       <c r="B835" s="54" t="s">
         <v>65</v>
       </c>
@@ -53896,7 +53895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="836" spans="2:28" hidden="1">
+    <row r="836" spans="2:28">
       <c r="B836" s="54" t="s">
         <v>65</v>
       </c>
@@ -54008,7 +54007,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="838" spans="2:28" hidden="1">
+    <row r="838" spans="2:28">
       <c r="B838" s="54" t="s">
         <v>65</v>
       </c>
@@ -54064,7 +54063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="839" spans="2:28" hidden="1">
+    <row r="839" spans="2:28">
       <c r="B839" s="54" t="s">
         <v>65</v>
       </c>
@@ -54126,7 +54125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="840" spans="2:28" hidden="1">
+    <row r="840" spans="2:28">
       <c r="B840" s="54" t="s">
         <v>65</v>
       </c>
@@ -54247,7 +54246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="842" spans="2:28" hidden="1">
+    <row r="842" spans="2:28">
       <c r="B842" s="54" t="s">
         <v>65</v>
       </c>
@@ -54303,7 +54302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="843" spans="2:28" hidden="1">
+    <row r="843" spans="2:28">
       <c r="B843" s="54" t="s">
         <v>65</v>
       </c>
@@ -54359,7 +54358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="844" spans="2:28" hidden="1">
+    <row r="844" spans="2:28">
       <c r="B844" s="54" t="s">
         <v>65</v>
       </c>
@@ -54418,7 +54417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="845" spans="2:28" hidden="1">
+    <row r="845" spans="2:28">
       <c r="B845" s="54" t="s">
         <v>65</v>
       </c>
@@ -54474,7 +54473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="846" spans="2:28" hidden="1">
+    <row r="846" spans="2:28">
       <c r="B846" s="54" t="s">
         <v>65</v>
       </c>
@@ -54530,7 +54529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="847" spans="2:28" hidden="1">
+    <row r="847" spans="2:28">
       <c r="B847" s="54" t="s">
         <v>65</v>
       </c>
@@ -54589,7 +54588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="848" spans="2:28" hidden="1">
+    <row r="848" spans="2:28">
       <c r="B848" s="54" t="s">
         <v>65</v>
       </c>
@@ -54651,7 +54650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="849" spans="2:30" hidden="1">
+    <row r="849" spans="2:30">
       <c r="B849" s="54" t="s">
         <v>65</v>
       </c>
@@ -54713,7 +54712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="850" spans="2:30" hidden="1">
+    <row r="850" spans="2:30">
       <c r="B850" s="54" t="s">
         <v>64</v>
       </c>
@@ -54769,7 +54768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="851" spans="2:30" hidden="1">
+    <row r="851" spans="2:30">
       <c r="B851" s="54" t="s">
         <v>64</v>
       </c>
@@ -54825,7 +54824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="852" spans="2:30" hidden="1">
+    <row r="852" spans="2:30">
       <c r="B852" s="54" t="s">
         <v>64</v>
       </c>
@@ -54899,7 +54898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="853" spans="2:30" hidden="1">
+    <row r="853" spans="2:30">
       <c r="B853" s="54" t="s">
         <v>64</v>
       </c>
@@ -55011,7 +55010,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="855" spans="2:30" hidden="1">
+    <row r="855" spans="2:30">
       <c r="B855" s="54" t="s">
         <v>64</v>
       </c>
@@ -55085,7 +55084,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="856" spans="2:30" hidden="1">
+    <row r="856" spans="2:30">
       <c r="B856" s="54" t="s">
         <v>64</v>
       </c>
@@ -55141,7 +55140,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="857" spans="2:30" hidden="1">
+    <row r="857" spans="2:30">
       <c r="B857" s="54" t="s">
         <v>64</v>
       </c>
@@ -55197,7 +55196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="858" spans="2:30" hidden="1">
+    <row r="858" spans="2:30">
       <c r="B858" s="54" t="s">
         <v>64</v>
       </c>
@@ -55259,7 +55258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="859" spans="2:30" hidden="1">
+    <row r="859" spans="2:30">
       <c r="B859" s="54" t="s">
         <v>64</v>
       </c>
@@ -55315,7 +55314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="860" spans="2:30" hidden="1">
+    <row r="860" spans="2:30">
       <c r="B860" s="54" t="s">
         <v>64</v>
       </c>
@@ -55427,7 +55426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="862" spans="2:30" hidden="1">
+    <row r="862" spans="2:30">
       <c r="B862" s="54" t="s">
         <v>64</v>
       </c>
@@ -55483,7 +55482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="863" spans="2:30" hidden="1">
+    <row r="863" spans="2:30">
       <c r="B863" s="54" t="s">
         <v>64</v>
       </c>
@@ -55539,7 +55538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="864" spans="2:30" hidden="1">
+    <row r="864" spans="2:30">
       <c r="B864" s="54" t="s">
         <v>64</v>
       </c>
@@ -55595,7 +55594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="865" spans="2:30" hidden="1">
+    <row r="865" spans="2:30">
       <c r="B865" s="54" t="s">
         <v>64</v>
       </c>
@@ -55651,7 +55650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="866" spans="2:30" hidden="1">
+    <row r="866" spans="2:30">
       <c r="B866" s="54" t="s">
         <v>64</v>
       </c>
@@ -55707,7 +55706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="867" spans="2:30" hidden="1">
+    <row r="867" spans="2:30">
       <c r="B867" s="54" t="s">
         <v>64</v>
       </c>
@@ -55763,7 +55762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="868" spans="2:30" hidden="1">
+    <row r="868" spans="2:30">
       <c r="B868" s="54" t="s">
         <v>64</v>
       </c>
@@ -55819,7 +55818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="869" spans="2:30" hidden="1">
+    <row r="869" spans="2:30">
       <c r="B869" s="54" t="s">
         <v>64</v>
       </c>
@@ -55875,7 +55874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="870" spans="2:30" hidden="1">
+    <row r="870" spans="2:30">
       <c r="B870" s="54" t="s">
         <v>64</v>
       </c>
@@ -55934,7 +55933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="871" spans="2:30" hidden="1">
+    <row r="871" spans="2:30">
       <c r="B871" s="54" t="s">
         <v>64</v>
       </c>
@@ -55993,7 +55992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="872" spans="2:30" hidden="1">
+    <row r="872" spans="2:30">
       <c r="B872" s="54" t="s">
         <v>64</v>
       </c>
@@ -56049,7 +56048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="873" spans="2:30" hidden="1">
+    <row r="873" spans="2:30">
       <c r="B873" s="54" t="s">
         <v>64</v>
       </c>
@@ -56105,7 +56104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="874" spans="2:30" hidden="1">
+    <row r="874" spans="2:30">
       <c r="B874" s="54" t="s">
         <v>64</v>
       </c>
@@ -56164,7 +56163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="875" spans="2:30" hidden="1">
+    <row r="875" spans="2:30">
       <c r="B875" s="54" t="s">
         <v>64</v>
       </c>
@@ -56220,7 +56219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="876" spans="2:30" hidden="1">
+    <row r="876" spans="2:30">
       <c r="B876" s="54" t="s">
         <v>64</v>
       </c>
@@ -56276,7 +56275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="877" spans="2:30" hidden="1">
+    <row r="877" spans="2:30">
       <c r="B877" s="54" t="s">
         <v>64</v>
       </c>
@@ -56335,7 +56334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="878" spans="2:30" hidden="1">
+    <row r="878" spans="2:30">
       <c r="B878" s="54" t="s">
         <v>64</v>
       </c>
@@ -56394,7 +56393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="879" spans="2:30" hidden="1">
+    <row r="879" spans="2:30">
       <c r="B879" s="54" t="s">
         <v>64</v>
       </c>
@@ -56453,7 +56452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="880" spans="2:30" hidden="1">
+    <row r="880" spans="2:30">
       <c r="B880" s="54" t="s">
         <v>64</v>
       </c>
@@ -56509,7 +56508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="881" spans="2:33" hidden="1">
+    <row r="881" spans="2:33">
       <c r="B881" s="54" t="s">
         <v>64</v>
       </c>
@@ -56577,7 +56576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="882" spans="2:33" hidden="1">
+    <row r="882" spans="2:33">
       <c r="B882" s="54" t="s">
         <v>64</v>
       </c>
@@ -56654,7 +56653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="883" spans="2:33" hidden="1">
+    <row r="883" spans="2:33">
       <c r="B883" s="54" t="s">
         <v>64</v>
       </c>
@@ -56713,7 +56712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="884" spans="2:33" hidden="1">
+    <row r="884" spans="2:33">
       <c r="B884" s="54" t="s">
         <v>64</v>
       </c>
@@ -56828,7 +56827,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="886" spans="2:33" hidden="1">
+    <row r="886" spans="2:33">
       <c r="B886" s="54" t="s">
         <v>64</v>
       </c>
@@ -56884,7 +56883,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="887" spans="2:33" hidden="1">
+    <row r="887" spans="2:33">
       <c r="B887" s="54" t="s">
         <v>64</v>
       </c>
@@ -56940,7 +56939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="888" spans="2:33" hidden="1">
+    <row r="888" spans="2:33">
       <c r="B888" s="54" t="s">
         <v>64</v>
       </c>
@@ -57011,7 +57010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="889" spans="2:33" hidden="1">
+    <row r="889" spans="2:33">
       <c r="B889" s="54" t="s">
         <v>64</v>
       </c>
@@ -57067,7 +57066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="890" spans="2:33" hidden="1">
+    <row r="890" spans="2:33">
       <c r="B890" s="54" t="s">
         <v>64</v>
       </c>
@@ -57123,7 +57122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="891" spans="2:33" hidden="1">
+    <row r="891" spans="2:33">
       <c r="B891" s="54" t="s">
         <v>64</v>
       </c>
@@ -57185,7 +57184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="892" spans="2:33" hidden="1">
+    <row r="892" spans="2:33">
       <c r="B892" s="54" t="s">
         <v>64</v>
       </c>
@@ -57241,7 +57240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="893" spans="2:33" hidden="1">
+    <row r="893" spans="2:33">
       <c r="B893" s="54" t="s">
         <v>64</v>
       </c>
@@ -57297,7 +57296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="894" spans="2:33" hidden="1">
+    <row r="894" spans="2:33">
       <c r="B894" s="54" t="s">
         <v>64</v>
       </c>
@@ -57353,7 +57352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="895" spans="2:33" hidden="1">
+    <row r="895" spans="2:33">
       <c r="B895" s="54" t="s">
         <v>64</v>
       </c>
@@ -57409,7 +57408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="896" spans="2:33" hidden="1">
+    <row r="896" spans="2:33">
       <c r="B896" s="54" t="s">
         <v>64</v>
       </c>
@@ -57521,7 +57520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="898" spans="2:31" hidden="1">
+    <row r="898" spans="2:31">
       <c r="B898" s="54" t="s">
         <v>64</v>
       </c>
@@ -57577,7 +57576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="899" spans="2:31" hidden="1">
+    <row r="899" spans="2:31">
       <c r="B899" s="54" t="s">
         <v>64</v>
       </c>
@@ -57633,7 +57632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="900" spans="2:31" hidden="1">
+    <row r="900" spans="2:31">
       <c r="B900" s="54" t="s">
         <v>64</v>
       </c>
@@ -57689,7 +57688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="901" spans="2:31" hidden="1">
+    <row r="901" spans="2:31">
       <c r="B901" s="54" t="s">
         <v>64</v>
       </c>
@@ -57745,7 +57744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="902" spans="2:31" hidden="1">
+    <row r="902" spans="2:31">
       <c r="B902" s="54" t="s">
         <v>64</v>
       </c>
@@ -57801,7 +57800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="903" spans="2:31" hidden="1">
+    <row r="903" spans="2:31">
       <c r="B903" s="54" t="s">
         <v>64</v>
       </c>
@@ -57857,7 +57856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="904" spans="2:31" hidden="1">
+    <row r="904" spans="2:31">
       <c r="B904" s="54" t="s">
         <v>64</v>
       </c>
@@ -57913,7 +57912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="905" spans="2:31" hidden="1">
+    <row r="905" spans="2:31">
       <c r="B905" s="54" t="s">
         <v>64</v>
       </c>
@@ -57972,7 +57971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="906" spans="2:31" hidden="1">
+    <row r="906" spans="2:31">
       <c r="B906" s="54" t="s">
         <v>65</v>
       </c>
@@ -58037,7 +58036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="907" spans="2:31" hidden="1">
+    <row r="907" spans="2:31">
       <c r="B907" s="54" t="s">
         <v>65</v>
       </c>
@@ -58102,7 +58101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="908" spans="2:31" hidden="1">
+    <row r="908" spans="2:31">
       <c r="B908" s="54" t="s">
         <v>65</v>
       </c>
@@ -58161,7 +58160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="909" spans="2:31" hidden="1">
+    <row r="909" spans="2:31">
       <c r="B909" s="54" t="s">
         <v>65</v>
       </c>
@@ -58282,7 +58281,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="911" spans="2:31" hidden="1">
+    <row r="911" spans="2:31">
       <c r="B911" s="54" t="s">
         <v>65</v>
       </c>
@@ -58338,7 +58337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="912" spans="2:31" hidden="1">
+    <row r="912" spans="2:31">
       <c r="B912" s="54" t="s">
         <v>65</v>
       </c>
@@ -58394,7 +58393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="913" spans="2:26" hidden="1">
+    <row r="913" spans="2:26">
       <c r="B913" s="54" t="s">
         <v>65</v>
       </c>
@@ -58450,7 +58449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="914" spans="2:26" hidden="1">
+    <row r="914" spans="2:26">
       <c r="B914" s="54" t="s">
         <v>65</v>
       </c>
@@ -58506,7 +58505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="915" spans="2:26" hidden="1">
+    <row r="915" spans="2:26">
       <c r="B915" s="54" t="s">
         <v>65</v>
       </c>
@@ -58562,7 +58561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="916" spans="2:26" hidden="1">
+    <row r="916" spans="2:26">
       <c r="B916" s="54" t="s">
         <v>65</v>
       </c>
@@ -58618,7 +58617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="917" spans="2:26" hidden="1">
+    <row r="917" spans="2:26">
       <c r="B917" s="54" t="s">
         <v>65</v>
       </c>
@@ -58674,7 +58673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="918" spans="2:26" hidden="1">
+    <row r="918" spans="2:26">
       <c r="B918" s="54" t="s">
         <v>65</v>
       </c>
@@ -58730,7 +58729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="919" spans="2:26" hidden="1">
+    <row r="919" spans="2:26">
       <c r="B919" s="54" t="s">
         <v>65</v>
       </c>
@@ -58786,7 +58785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="920" spans="2:26" hidden="1">
+    <row r="920" spans="2:26">
       <c r="B920" s="54" t="s">
         <v>65</v>
       </c>
@@ -58842,7 +58841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="921" spans="2:26" hidden="1">
+    <row r="921" spans="2:26">
       <c r="B921" s="54" t="s">
         <v>65</v>
       </c>
@@ -58898,7 +58897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="922" spans="2:26" hidden="1">
+    <row r="922" spans="2:26">
       <c r="B922" s="54" t="s">
         <v>65</v>
       </c>
@@ -58954,7 +58953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="923" spans="2:26" hidden="1">
+    <row r="923" spans="2:26">
       <c r="B923" s="54" t="s">
         <v>65</v>
       </c>
@@ -59010,7 +59009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="924" spans="2:26" hidden="1">
+    <row r="924" spans="2:26">
       <c r="B924" s="54" t="s">
         <v>65</v>
       </c>
@@ -59069,7 +59068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="925" spans="2:26" hidden="1">
+    <row r="925" spans="2:26">
       <c r="B925" s="54" t="s">
         <v>65</v>
       </c>
@@ -59131,7 +59130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="926" spans="2:26" hidden="1">
+    <row r="926" spans="2:26">
       <c r="B926" s="54" t="s">
         <v>65</v>
       </c>
@@ -59187,7 +59186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="927" spans="2:26" hidden="1">
+    <row r="927" spans="2:26">
       <c r="B927" s="54" t="s">
         <v>65</v>
       </c>
@@ -59243,7 +59242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="928" spans="2:26" hidden="1">
+    <row r="928" spans="2:26">
       <c r="B928" s="54" t="s">
         <v>65</v>
       </c>
@@ -59299,7 +59298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="929" spans="2:29" hidden="1">
+    <row r="929" spans="2:29">
       <c r="B929" s="54" t="s">
         <v>65</v>
       </c>
@@ -59355,7 +59354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="930" spans="2:29" hidden="1">
+    <row r="930" spans="2:29">
       <c r="B930" s="54" t="s">
         <v>65</v>
       </c>
@@ -59411,7 +59410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="931" spans="2:29" hidden="1">
+    <row r="931" spans="2:29">
       <c r="B931" s="54" t="s">
         <v>65</v>
       </c>
@@ -59467,7 +59466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="932" spans="2:29" hidden="1">
+    <row r="932" spans="2:29">
       <c r="B932" s="54" t="s">
         <v>64</v>
       </c>
@@ -59591,7 +59590,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="934" spans="2:29" hidden="1">
+    <row r="934" spans="2:29">
       <c r="B934" s="54" t="s">
         <v>64</v>
       </c>
@@ -59647,7 +59646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="935" spans="2:29" hidden="1">
+    <row r="935" spans="2:29">
       <c r="B935" s="54" t="s">
         <v>64</v>
       </c>
@@ -59706,7 +59705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="936" spans="2:29" hidden="1">
+    <row r="936" spans="2:29">
       <c r="B936" s="54" t="s">
         <v>64</v>
       </c>
@@ -59762,7 +59761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="937" spans="2:29" hidden="1">
+    <row r="937" spans="2:29">
       <c r="B937" s="54" t="s">
         <v>64</v>
       </c>
@@ -59818,7 +59817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="938" spans="2:29" hidden="1">
+    <row r="938" spans="2:29">
       <c r="B938" s="54" t="s">
         <v>64</v>
       </c>
@@ -59874,7 +59873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="939" spans="2:29" hidden="1">
+    <row r="939" spans="2:29">
       <c r="B939" s="54" t="s">
         <v>64</v>
       </c>
@@ -59930,7 +59929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="940" spans="2:29" hidden="1">
+    <row r="940" spans="2:29">
       <c r="B940" s="54" t="s">
         <v>64</v>
       </c>
@@ -59986,7 +59985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="941" spans="2:29" hidden="1">
+    <row r="941" spans="2:29">
       <c r="B941" s="54" t="s">
         <v>64</v>
       </c>
@@ -60045,7 +60044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="942" spans="2:29" hidden="1">
+    <row r="942" spans="2:29">
       <c r="B942" s="54" t="s">
         <v>64</v>
       </c>
@@ -60101,7 +60100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="943" spans="2:29" hidden="1">
+    <row r="943" spans="2:29">
       <c r="B943" s="54" t="s">
         <v>64</v>
       </c>
@@ -60157,7 +60156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="944" spans="2:29" hidden="1">
+    <row r="944" spans="2:29">
       <c r="B944" s="54" t="s">
         <v>64</v>
       </c>
@@ -60216,7 +60215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="945" spans="2:32" hidden="1">
+    <row r="945" spans="2:32">
       <c r="B945" s="54" t="s">
         <v>64</v>
       </c>
@@ -60272,7 +60271,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="946" spans="2:32" hidden="1">
+    <row r="946" spans="2:32">
       <c r="B946" s="54" t="s">
         <v>64</v>
       </c>
@@ -60328,7 +60327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="947" spans="2:32" hidden="1">
+    <row r="947" spans="2:32">
       <c r="B947" s="54" t="s">
         <v>64</v>
       </c>
@@ -60387,7 +60386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="948" spans="2:32" hidden="1">
+    <row r="948" spans="2:32">
       <c r="B948" s="54" t="s">
         <v>64</v>
       </c>
@@ -60446,7 +60445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="949" spans="2:32" hidden="1">
+    <row r="949" spans="2:32">
       <c r="B949" s="54" t="s">
         <v>64</v>
       </c>
@@ -60505,7 +60504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="950" spans="2:32" hidden="1">
+    <row r="950" spans="2:32">
       <c r="B950" s="54" t="s">
         <v>64</v>
       </c>
@@ -60564,7 +60563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="951" spans="2:32" hidden="1">
+    <row r="951" spans="2:32">
       <c r="B951" s="54" t="s">
         <v>64</v>
       </c>
@@ -60620,7 +60619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="952" spans="2:32" hidden="1">
+    <row r="952" spans="2:32">
       <c r="B952" s="54" t="s">
         <v>64</v>
       </c>
@@ -60676,7 +60675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="2:32" hidden="1">
+    <row r="953" spans="2:32">
       <c r="B953" s="54" t="s">
         <v>65</v>
       </c>
@@ -60747,7 +60746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="954" spans="2:32" hidden="1">
+    <row r="954" spans="2:32">
       <c r="B954" s="54" t="s">
         <v>65</v>
       </c>
@@ -60874,7 +60873,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="956" spans="2:32" hidden="1">
+    <row r="956" spans="2:32">
       <c r="B956" s="54" t="s">
         <v>65</v>
       </c>
@@ -60930,7 +60929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="957" spans="2:32" hidden="1">
+    <row r="957" spans="2:32">
       <c r="B957" s="54" t="s">
         <v>65</v>
       </c>
@@ -60986,7 +60985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="958" spans="2:32" hidden="1">
+    <row r="958" spans="2:32">
       <c r="B958" s="54" t="s">
         <v>65</v>
       </c>
@@ -61042,7 +61041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="959" spans="2:32" hidden="1">
+    <row r="959" spans="2:32">
       <c r="B959" s="54" t="s">
         <v>65</v>
       </c>
@@ -61098,7 +61097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="960" spans="2:32" hidden="1">
+    <row r="960" spans="2:32">
       <c r="B960" s="54" t="s">
         <v>65</v>
       </c>
@@ -61154,7 +61153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="961" spans="2:26" hidden="1">
+    <row r="961" spans="2:26">
       <c r="B961" s="54" t="s">
         <v>65</v>
       </c>
@@ -61210,7 +61209,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="962" spans="2:26" hidden="1">
+    <row r="962" spans="2:26">
       <c r="B962" s="54" t="s">
         <v>65</v>
       </c>
@@ -61269,7 +61268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="963" spans="2:26" hidden="1">
+    <row r="963" spans="2:26">
       <c r="B963" s="54" t="s">
         <v>65</v>
       </c>
@@ -61325,7 +61324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="964" spans="2:26" hidden="1">
+    <row r="964" spans="2:26">
       <c r="B964" s="54" t="s">
         <v>65</v>
       </c>
@@ -61381,7 +61380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="965" spans="2:26" hidden="1">
+    <row r="965" spans="2:26">
       <c r="B965" s="54" t="s">
         <v>65</v>
       </c>
@@ -61437,7 +61436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="966" spans="2:26" hidden="1">
+    <row r="966" spans="2:26">
       <c r="B966" s="54" t="s">
         <v>65</v>
       </c>
@@ -61552,7 +61551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="968" spans="2:26" hidden="1">
+    <row r="968" spans="2:26">
       <c r="B968" s="54" t="s">
         <v>65</v>
       </c>
@@ -61608,7 +61607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="969" spans="2:26" hidden="1">
+    <row r="969" spans="2:26">
       <c r="B969" s="54" t="s">
         <v>65</v>
       </c>
@@ -61667,7 +61666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="970" spans="2:26" hidden="1">
+    <row r="970" spans="2:26">
       <c r="B970" s="54" t="s">
         <v>65</v>
       </c>
@@ -61726,7 +61725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="971" spans="2:26" hidden="1">
+    <row r="971" spans="2:26">
       <c r="B971" s="54" t="s">
         <v>65</v>
       </c>
@@ -61782,7 +61781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="972" spans="2:26" hidden="1">
+    <row r="972" spans="2:26">
       <c r="B972" s="54" t="s">
         <v>65</v>
       </c>
@@ -61841,7 +61840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="973" spans="2:26" hidden="1">
+    <row r="973" spans="2:26">
       <c r="B973" s="54" t="s">
         <v>65</v>
       </c>
@@ -61897,7 +61896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="974" spans="2:26" hidden="1">
+    <row r="974" spans="2:26">
       <c r="B974" s="54" t="s">
         <v>65</v>
       </c>
@@ -61959,7 +61958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="975" spans="2:26" hidden="1">
+    <row r="975" spans="2:26">
       <c r="B975" s="54" t="s">
         <v>65</v>
       </c>
@@ -62015,7 +62014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="976" spans="2:26" hidden="1">
+    <row r="976" spans="2:26">
       <c r="B976" s="54" t="s">
         <v>65</v>
       </c>
@@ -62071,7 +62070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="977" spans="1:29" hidden="1">
+    <row r="977" spans="1:29">
       <c r="B977" s="54" t="s">
         <v>65</v>
       </c>
@@ -62127,7 +62126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="978" spans="1:29" customFormat="1" hidden="1">
+    <row r="978" spans="1:29" customFormat="1">
       <c r="A978" s="4"/>
       <c r="B978" s="54" t="s">
         <v>65</v>
@@ -62187,7 +62186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="979" spans="1:29" customFormat="1" hidden="1">
+    <row r="979" spans="1:29" customFormat="1">
       <c r="A979" s="4"/>
       <c r="B979" s="54" t="s">
         <v>65</v>
@@ -62250,7 +62249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="980" spans="1:29" customFormat="1" hidden="1">
+    <row r="980" spans="1:29" customFormat="1">
       <c r="A980" s="4"/>
       <c r="B980" s="54" t="s">
         <v>65</v>
@@ -62313,7 +62312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="981" spans="1:29" customFormat="1" hidden="1">
+    <row r="981" spans="1:29" customFormat="1">
       <c r="A981" s="4"/>
       <c r="B981" s="54" t="s">
         <v>65</v>
@@ -62370,7 +62369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="982" spans="1:29" customFormat="1" hidden="1">
+    <row r="982" spans="1:29" customFormat="1">
       <c r="A982" s="4"/>
       <c r="B982" s="54" t="s">
         <v>65</v>
@@ -62442,7 +62441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="983" spans="1:29" customFormat="1" hidden="1">
+    <row r="983" spans="1:29" customFormat="1">
       <c r="A983" s="4"/>
       <c r="B983" s="54" t="s">
         <v>65</v>
@@ -62499,7 +62498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="984" spans="1:29" customFormat="1" hidden="1">
+    <row r="984" spans="1:29" customFormat="1">
       <c r="A984" s="4"/>
       <c r="B984" s="54" t="s">
         <v>65</v>
@@ -62613,7 +62612,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="986" spans="1:29" customFormat="1" hidden="1">
+    <row r="986" spans="1:29" customFormat="1">
       <c r="A986" s="4"/>
       <c r="B986" s="54" t="s">
         <v>65</v>
@@ -62670,7 +62669,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="987" spans="1:29" customFormat="1" hidden="1">
+    <row r="987" spans="1:29" customFormat="1">
       <c r="A987" s="4"/>
       <c r="B987" s="54" t="s">
         <v>65</v>
@@ -62730,7 +62729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="988" spans="1:29" customFormat="1" hidden="1">
+    <row r="988" spans="1:29" customFormat="1">
       <c r="A988" s="4"/>
       <c r="B988" s="54" t="s">
         <v>65</v>
@@ -62787,7 +62786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="989" spans="1:29" customFormat="1" hidden="1">
+    <row r="989" spans="1:29" customFormat="1">
       <c r="A989" s="4"/>
       <c r="B989" s="54" t="s">
         <v>65</v>
@@ -62847,7 +62846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="990" spans="1:29" customFormat="1" hidden="1">
+    <row r="990" spans="1:29" customFormat="1">
       <c r="A990" s="4"/>
       <c r="B990" s="54" t="s">
         <v>65</v>
@@ -62904,7 +62903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="991" spans="1:29" customFormat="1" hidden="1">
+    <row r="991" spans="1:29" customFormat="1">
       <c r="A991" s="4"/>
       <c r="B991" s="54" t="s">
         <v>65</v>
@@ -62961,7 +62960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="992" spans="1:29" customFormat="1" hidden="1">
+    <row r="992" spans="1:29" customFormat="1">
       <c r="A992" s="4"/>
       <c r="B992" s="54" t="s">
         <v>65</v>
@@ -63027,7 +63026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="993" spans="1:27" customFormat="1" hidden="1">
+    <row r="993" spans="1:27" customFormat="1">
       <c r="A993" s="4"/>
       <c r="B993" s="54" t="s">
         <v>65</v>
@@ -63087,7 +63086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="994" spans="1:27" customFormat="1" hidden="1">
+    <row r="994" spans="1:27" customFormat="1">
       <c r="A994" s="4"/>
       <c r="B994" s="54" t="s">
         <v>65</v>
@@ -63162,7 +63161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="995" spans="1:27" customFormat="1" hidden="1">
+    <row r="995" spans="1:27" customFormat="1">
       <c r="A995" s="4"/>
       <c r="B995" s="54" t="s">
         <v>65</v>
@@ -63219,7 +63218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="996" spans="1:27" customFormat="1" hidden="1">
+    <row r="996" spans="1:27" customFormat="1">
       <c r="A996" s="4"/>
       <c r="B996" s="54" t="s">
         <v>65</v>
@@ -63276,7 +63275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="997" spans="1:27" customFormat="1" hidden="1">
+    <row r="997" spans="1:27" customFormat="1">
       <c r="A997" s="4"/>
       <c r="B997" s="54" t="s">
         <v>65</v>
@@ -63333,7 +63332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="998" spans="1:27" customFormat="1" hidden="1">
+    <row r="998" spans="1:27" customFormat="1">
       <c r="A998" s="4"/>
       <c r="B998" s="54" t="s">
         <v>65</v>
@@ -63450,7 +63449,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1000" spans="1:27" customFormat="1" hidden="1">
+    <row r="1000" spans="1:27" customFormat="1">
       <c r="A1000" s="4"/>
       <c r="B1000" s="54" t="s">
         <v>65</v>
@@ -63507,7 +63506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1001" spans="1:27" customFormat="1" hidden="1">
+    <row r="1001" spans="1:27" customFormat="1">
       <c r="A1001" s="4"/>
       <c r="B1001" s="54" t="s">
         <v>65</v>
@@ -63564,7 +63563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1002" spans="1:27" customFormat="1" hidden="1">
+    <row r="1002" spans="1:27" customFormat="1">
       <c r="A1002" s="4"/>
       <c r="B1002" s="54" t="s">
         <v>64</v>
@@ -63624,7 +63623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1003" spans="1:27" customFormat="1" hidden="1">
+    <row r="1003" spans="1:27" customFormat="1">
       <c r="A1003" s="4"/>
       <c r="B1003" s="54" t="s">
         <v>64</v>
@@ -63684,7 +63683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1004" spans="1:27" customFormat="1" hidden="1">
+    <row r="1004" spans="1:27" customFormat="1">
       <c r="A1004" s="4"/>
       <c r="B1004" s="54" t="s">
         <v>64</v>
@@ -63804,7 +63803,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="1006" spans="1:27" customFormat="1" hidden="1">
+    <row r="1006" spans="1:27" customFormat="1">
       <c r="A1006" s="4"/>
       <c r="B1006" s="54" t="s">
         <v>64</v>
@@ -63861,7 +63860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1007" spans="1:27" customFormat="1" hidden="1">
+    <row r="1007" spans="1:27" customFormat="1">
       <c r="A1007" s="4"/>
       <c r="B1007" s="54" t="s">
         <v>64</v>
@@ -63918,7 +63917,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="1008" spans="1:27" customFormat="1" hidden="1">
+    <row r="1008" spans="1:27" customFormat="1">
       <c r="A1008" s="4"/>
       <c r="B1008" s="54" t="s">
         <v>64</v>
@@ -63990,7 +63989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1009" spans="1:28" customFormat="1" hidden="1">
+    <row r="1009" spans="1:28" customFormat="1">
       <c r="A1009" s="4"/>
       <c r="B1009" s="54" t="s">
         <v>64</v>
@@ -64047,7 +64046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1010" spans="1:28" customFormat="1" hidden="1">
+    <row r="1010" spans="1:28" customFormat="1">
       <c r="A1010" s="4"/>
       <c r="B1010" s="54" t="s">
         <v>64</v>
@@ -64104,7 +64103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1011" spans="1:28" customFormat="1" hidden="1">
+    <row r="1011" spans="1:28" customFormat="1">
       <c r="A1011" s="4"/>
       <c r="B1011" s="54" t="s">
         <v>64</v>
@@ -64161,7 +64160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1012" spans="1:28" customFormat="1" hidden="1">
+    <row r="1012" spans="1:28" customFormat="1">
       <c r="A1012" s="4"/>
       <c r="B1012" s="54" t="s">
         <v>64</v>
@@ -64218,7 +64217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1013" spans="1:28" customFormat="1" hidden="1">
+    <row r="1013" spans="1:28" customFormat="1">
       <c r="A1013" s="4"/>
       <c r="B1013" s="54" t="s">
         <v>64</v>
@@ -64281,7 +64280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1014" spans="1:28" customFormat="1" hidden="1">
+    <row r="1014" spans="1:28" customFormat="1">
       <c r="A1014" s="4"/>
       <c r="B1014" s="54" t="s">
         <v>64</v>
@@ -64347,7 +64346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1015" spans="1:28" customFormat="1" hidden="1">
+    <row r="1015" spans="1:28" customFormat="1">
       <c r="A1015" s="4"/>
       <c r="B1015" s="54" t="s">
         <v>64</v>
@@ -64419,7 +64418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1016" spans="1:28" customFormat="1" hidden="1">
+    <row r="1016" spans="1:28" customFormat="1">
       <c r="A1016" s="4"/>
       <c r="B1016" s="54" t="s">
         <v>64</v>
@@ -64476,7 +64475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1017" spans="1:28" customFormat="1" hidden="1">
+    <row r="1017" spans="1:28" customFormat="1">
       <c r="A1017" s="4"/>
       <c r="B1017" s="54" t="s">
         <v>64</v>
@@ -64533,7 +64532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1018" spans="1:28" customFormat="1" hidden="1">
+    <row r="1018" spans="1:28" customFormat="1">
       <c r="A1018" s="4"/>
       <c r="B1018" s="54" t="s">
         <v>64</v>
@@ -64590,7 +64589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1019" spans="1:28" customFormat="1" hidden="1">
+    <row r="1019" spans="1:28" customFormat="1">
       <c r="A1019" s="4"/>
       <c r="B1019" s="54" t="s">
         <v>64</v>
@@ -64662,7 +64661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1020" spans="1:28" customFormat="1" hidden="1">
+    <row r="1020" spans="1:28" customFormat="1">
       <c r="A1020" s="4"/>
       <c r="B1020" s="54" t="s">
         <v>64</v>
@@ -64719,7 +64718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1021" spans="1:28" customFormat="1" hidden="1">
+    <row r="1021" spans="1:28" customFormat="1">
       <c r="A1021" s="4"/>
       <c r="B1021" s="54" t="s">
         <v>64</v>
@@ -64833,7 +64832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1023" spans="1:28" customFormat="1" hidden="1">
+    <row r="1023" spans="1:28" customFormat="1">
       <c r="A1023" s="4"/>
       <c r="B1023" s="54" t="s">
         <v>64</v>
@@ -64890,7 +64889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1024" spans="1:28" customFormat="1" hidden="1">
+    <row r="1024" spans="1:28" customFormat="1">
       <c r="A1024" s="4"/>
       <c r="B1024" s="54" t="s">
         <v>64</v>
@@ -64947,7 +64946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1025" spans="1:26" customFormat="1" hidden="1">
+    <row r="1025" spans="1:26" customFormat="1">
       <c r="A1025" s="4"/>
       <c r="B1025" s="54" t="s">
         <v>64</v>
@@ -65004,7 +65003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1026" spans="1:26" customFormat="1" hidden="1">
+    <row r="1026" spans="1:26" customFormat="1">
       <c r="A1026" s="4"/>
       <c r="B1026" s="54" t="s">
         <v>64</v>
@@ -65076,7 +65075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1027" spans="1:26" customFormat="1" hidden="1">
+    <row r="1027" spans="1:26" customFormat="1">
       <c r="A1027" s="4"/>
       <c r="B1027" s="54" t="s">
         <v>64</v>
@@ -65250,7 +65249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1030" spans="1:26" customFormat="1" hidden="1">
+    <row r="1030" spans="1:26" customFormat="1">
       <c r="A1030" s="4"/>
       <c r="B1030" s="54" t="s">
         <v>64</v>
@@ -65307,7 +65306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1031" spans="1:26" customFormat="1" hidden="1">
+    <row r="1031" spans="1:26" customFormat="1">
       <c r="A1031" s="4"/>
       <c r="B1031" s="54" t="s">
         <v>64</v>
@@ -65364,7 +65363,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1032" spans="1:26" customFormat="1" hidden="1">
+    <row r="1032" spans="1:26" customFormat="1">
       <c r="A1032" s="4"/>
       <c r="B1032" s="54" t="s">
         <v>64</v>
@@ -65421,7 +65420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1033" spans="1:26" customFormat="1" hidden="1">
+    <row r="1033" spans="1:26" customFormat="1">
       <c r="A1033" s="4"/>
       <c r="B1033" s="54" t="s">
         <v>64</v>
@@ -65493,7 +65492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1034" spans="1:26" customFormat="1" hidden="1">
+    <row r="1034" spans="1:26" customFormat="1">
       <c r="A1034" s="4"/>
       <c r="B1034" s="54" t="s">
         <v>64</v>
@@ -65550,7 +65549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1035" spans="1:26" customFormat="1" hidden="1">
+    <row r="1035" spans="1:26" customFormat="1">
       <c r="A1035" s="4"/>
       <c r="B1035" s="54" t="s">
         <v>64</v>
@@ -65607,7 +65606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1036" spans="1:26" customFormat="1" hidden="1">
+    <row r="1036" spans="1:26" customFormat="1">
       <c r="A1036" s="4"/>
       <c r="B1036" s="54" t="s">
         <v>64</v>
@@ -65670,7 +65669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1037" spans="1:26" customFormat="1" hidden="1">
+    <row r="1037" spans="1:26" customFormat="1">
       <c r="A1037" s="4"/>
       <c r="B1037" s="54" t="s">
         <v>64</v>
@@ -65727,7 +65726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1038" spans="1:26" customFormat="1" hidden="1">
+    <row r="1038" spans="1:26" customFormat="1">
       <c r="A1038" s="4"/>
       <c r="B1038" s="54" t="s">
         <v>64</v>
@@ -65784,7 +65783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1039" spans="1:26" customFormat="1" hidden="1">
+    <row r="1039" spans="1:26" customFormat="1">
       <c r="A1039" s="4"/>
       <c r="B1039" s="54" t="s">
         <v>64</v>
@@ -65841,7 +65840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1040" spans="1:26" customFormat="1" hidden="1">
+    <row r="1040" spans="1:26" customFormat="1">
       <c r="A1040" s="4"/>
       <c r="B1040" s="54" t="s">
         <v>64</v>
@@ -65901,7 +65900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1041" spans="1:28" customFormat="1" hidden="1">
+    <row r="1041" spans="1:28" customFormat="1">
       <c r="A1041" s="4"/>
       <c r="B1041" s="54" t="s">
         <v>64</v>
@@ -65961,7 +65960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1042" spans="1:28" customFormat="1" hidden="1">
+    <row r="1042" spans="1:28" customFormat="1">
       <c r="A1042" s="4"/>
       <c r="B1042" s="54" t="s">
         <v>64</v>
@@ -66021,7 +66020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1043" spans="1:28" customFormat="1" hidden="1">
+    <row r="1043" spans="1:28" customFormat="1">
       <c r="A1043" s="4"/>
       <c r="B1043" s="54" t="s">
         <v>64</v>
@@ -66081,7 +66080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1044" spans="1:28" customFormat="1" hidden="1">
+    <row r="1044" spans="1:28" customFormat="1">
       <c r="A1044" s="4"/>
       <c r="B1044" s="54" t="s">
         <v>64</v>
@@ -66138,7 +66137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1045" spans="1:28" customFormat="1" hidden="1">
+    <row r="1045" spans="1:28" customFormat="1">
       <c r="A1045" s="4"/>
       <c r="B1045" s="54" t="s">
         <v>64</v>
@@ -66195,7 +66194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1046" spans="1:28" customFormat="1" hidden="1">
+    <row r="1046" spans="1:28" customFormat="1">
       <c r="A1046" s="4"/>
       <c r="B1046" s="54" t="s">
         <v>64</v>
@@ -66252,7 +66251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1047" spans="1:28" customFormat="1" hidden="1">
+    <row r="1047" spans="1:28" customFormat="1">
       <c r="A1047" s="4"/>
       <c r="B1047" s="54" t="s">
         <v>64</v>
@@ -66309,7 +66308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1048" spans="1:28" customFormat="1" hidden="1">
+    <row r="1048" spans="1:28" customFormat="1">
       <c r="A1048" s="4"/>
       <c r="B1048" s="54" t="s">
         <v>64</v>
@@ -66366,7 +66365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1049" spans="1:28" customFormat="1" hidden="1">
+    <row r="1049" spans="1:28" customFormat="1">
       <c r="A1049" s="4"/>
       <c r="B1049" s="54" t="s">
         <v>64</v>
@@ -66423,7 +66422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1050" spans="1:28" customFormat="1" hidden="1">
+    <row r="1050" spans="1:28" customFormat="1">
       <c r="A1050" s="4"/>
       <c r="B1050" s="54" t="s">
         <v>64</v>
@@ -66480,7 +66479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1051" spans="1:28" customFormat="1" hidden="1">
+    <row r="1051" spans="1:28" customFormat="1">
       <c r="A1051" s="4"/>
       <c r="B1051" s="54" t="s">
         <v>136</v>
@@ -66540,7 +66539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1052" spans="1:28" customFormat="1" hidden="1">
+    <row r="1052" spans="1:28" customFormat="1">
       <c r="A1052" s="4"/>
       <c r="B1052" s="54" t="s">
         <v>136</v>
@@ -66606,7 +66605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1053" spans="1:28" customFormat="1" hidden="1">
+    <row r="1053" spans="1:28" customFormat="1">
       <c r="A1053" s="4"/>
       <c r="B1053" s="54" t="s">
         <v>136</v>
@@ -66783,7 +66782,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="1056" spans="1:28" customFormat="1" hidden="1">
+    <row r="1056" spans="1:28" customFormat="1">
       <c r="A1056" s="4"/>
       <c r="B1056" s="54" t="s">
         <v>136</v>
@@ -66858,7 +66857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1057" spans="1:26" customFormat="1" hidden="1">
+    <row r="1057" spans="1:26" customFormat="1">
       <c r="A1057" s="4"/>
       <c r="B1057" s="54" t="s">
         <v>136</v>
@@ -66915,7 +66914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1058" spans="1:26" customFormat="1" hidden="1">
+    <row r="1058" spans="1:26" customFormat="1">
       <c r="A1058" s="4"/>
       <c r="B1058" s="54" t="s">
         <v>136</v>
@@ -66972,7 +66971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1059" spans="1:26" customFormat="1" hidden="1">
+    <row r="1059" spans="1:26" customFormat="1">
       <c r="A1059" s="4"/>
       <c r="B1059" s="54" t="s">
         <v>136</v>
@@ -67029,7 +67028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1060" spans="1:26" customFormat="1" hidden="1">
+    <row r="1060" spans="1:26" customFormat="1">
       <c r="A1060" s="4"/>
       <c r="B1060" s="54" t="s">
         <v>136</v>
@@ -67086,7 +67085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1061" spans="1:26" customFormat="1" hidden="1">
+    <row r="1061" spans="1:26" customFormat="1">
       <c r="A1061" s="4"/>
       <c r="B1061" s="54" t="s">
         <v>136</v>
@@ -67143,7 +67142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1062" spans="1:26" customFormat="1" hidden="1">
+    <row r="1062" spans="1:26" customFormat="1">
       <c r="A1062" s="4"/>
       <c r="B1062" s="54" t="s">
         <v>136</v>
@@ -67200,7 +67199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1063" spans="1:26" customFormat="1" hidden="1">
+    <row r="1063" spans="1:26" customFormat="1">
       <c r="A1063" s="4"/>
       <c r="B1063" s="54" t="s">
         <v>136</v>
@@ -67257,7 +67256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1064" spans="1:26" customFormat="1" hidden="1">
+    <row r="1064" spans="1:26" customFormat="1">
       <c r="A1064" s="4"/>
       <c r="B1064" s="54" t="s">
         <v>136</v>
@@ -67317,7 +67316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1065" spans="1:26" customFormat="1" hidden="1">
+    <row r="1065" spans="1:26" customFormat="1">
       <c r="A1065" s="4"/>
       <c r="B1065" s="54" t="s">
         <v>136</v>
@@ -67377,7 +67376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1066" spans="1:26" customFormat="1" hidden="1">
+    <row r="1066" spans="1:26" customFormat="1">
       <c r="A1066" s="4"/>
       <c r="B1066" s="54" t="s">
         <v>136</v>
@@ -67437,7 +67436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1067" spans="1:26" customFormat="1" hidden="1">
+    <row r="1067" spans="1:26" customFormat="1">
       <c r="A1067" s="4"/>
       <c r="B1067" s="54" t="s">
         <v>136</v>
@@ -67776,14 +67775,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1"/>
-  <autoFilter ref="Q1:Q1067" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Mesocentrotus franciscanus"/>
-        <filter val="Pomaulax gibberosus"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="Q1:Q1067" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 O3:O4 O6:O112 O905:O65536 O114:O880" xr:uid="{00000000-0002-0000-0100-000000000000}">

--- a/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
+++ b/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alecjones/Documents/GitHub/Alec_Jones_Honours/Jones_honours/01_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D49540-2723-C24B-B5AE-FFEDC7B09620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C279271B-B442-2446-BABB-176737D5FB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="22500" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28080" yWindow="4440" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMARY" sheetId="13" state="hidden" r:id="rId1"/>

--- a/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
+++ b/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alecjones/Documents/GitHub/Alec_Jones_Honours/Jones_honours/01_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C279271B-B442-2446-BABB-176737D5FB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF67E4A-40C1-554A-BC8A-4499D7CACF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28080" yWindow="4440" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4960" yWindow="1340" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMARY" sheetId="13" state="hidden" r:id="rId1"/>

--- a/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
+++ b/Jones_honours/01_raw_data/RLS_CANADA_Bamfield_2021.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alecjones/Documents/GitHub/Alec_Jones_Honours/Jones_honours/01_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF67E4A-40C1-554A-BC8A-4499D7CACF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5594CA-E60D-4E45-810C-0A9030419350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="1340" windowWidth="27380" windowHeight="14240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="900" windowWidth="27380" windowHeight="14260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMARY" sheetId="13" state="hidden" r:id="rId1"/>
@@ -29,8 +29,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="158" r:id="rId9"/>
-    <pivotCache cacheId="159" r:id="rId10"/>
+    <pivotCache cacheId="4" r:id="rId9"/>
+    <pivotCache cacheId="5" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3316,7 +3316,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="158" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="4" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="4" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:E46" firstHeaderRow="1" firstDataRow="4" firstDataCol="2"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
@@ -3564,7 +3564,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="159" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000001000000}" name="PivotTable2" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="5" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:I8" firstHeaderRow="1" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="48">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
